--- a/data/SingleCell_Pipeline_MasterSchema.xlsx
+++ b/data/SingleCell_Pipeline_MasterSchema.xlsx
@@ -23,6 +23,8 @@
     <sheet name="Order_Totals" sheetId="13" state="visible" r:id="rId15"/>
     <sheet name="Buffer_Recipes" sheetId="14" state="visible" r:id="rId16"/>
     <sheet name="Unit_Conversions" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="Oligo_Catalog" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="Antibody_Catalog" sheetId="17" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="12" name="_xlnm._FilterDatabase" vbProcedure="false">Order_Totals!$A$1:$F$73</definedName>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2807" uniqueCount="1066">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2893" uniqueCount="1130">
   <si>
     <t xml:space="preserve">Experiment inputs</t>
   </si>
@@ -3237,6 +3239,198 @@
   </si>
   <si>
     <t xml:space="preserve">lane-rxn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oligo_Catalog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin-only. Sequencing/index oligos (e.g. RPIxx, D7xx). Fill in vendor/catalog#/price. IDs are placeholders (OL###).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antibody_Catalog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin-only. Flow antibodies, HTOs, and TotalSeq staining cocktails. Fill in vendor/catalog#/price. IDs are placeholders (AB###).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB030</t>
   </si>
 </sst>
 </file>
@@ -3258,7 +3452,7 @@
     <numFmt numFmtId="175" formatCode="\$#,##0.00####"/>
     <numFmt numFmtId="176" formatCode="0.#####"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="44">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3570,6 +3764,14 @@
       <family val="1"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF2E4A62"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -3767,7 +3969,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="120">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3828,7 +4030,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4240,6 +4442,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19515,6 +19725,458 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="118" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="119" t="s">
+        <v>322</v>
+      </c>
+      <c r="B4" s="119" t="s">
+        <v>323</v>
+      </c>
+      <c r="C4" s="119" t="s">
+        <v>324</v>
+      </c>
+      <c r="D4" s="119" t="s">
+        <v>325</v>
+      </c>
+      <c r="E4" s="119" t="s">
+        <v>326</v>
+      </c>
+      <c r="F4" s="119" t="s">
+        <v>126</v>
+      </c>
+      <c r="G4" s="119" t="s">
+        <v>327</v>
+      </c>
+      <c r="H4" s="119" t="s">
+        <v>328</v>
+      </c>
+      <c r="I4" s="119" t="s">
+        <v>329</v>
+      </c>
+      <c r="J4" s="119" t="s">
+        <v>330</v>
+      </c>
+      <c r="K4" s="119" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="118" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="119" t="s">
+        <v>322</v>
+      </c>
+      <c r="B4" s="119" t="s">
+        <v>323</v>
+      </c>
+      <c r="C4" s="119" t="s">
+        <v>324</v>
+      </c>
+      <c r="D4" s="119" t="s">
+        <v>325</v>
+      </c>
+      <c r="E4" s="119" t="s">
+        <v>326</v>
+      </c>
+      <c r="F4" s="119" t="s">
+        <v>126</v>
+      </c>
+      <c r="G4" s="119" t="s">
+        <v>327</v>
+      </c>
+      <c r="H4" s="119" t="s">
+        <v>328</v>
+      </c>
+      <c r="I4" s="119" t="s">
+        <v>329</v>
+      </c>
+      <c r="J4" s="119" t="s">
+        <v>330</v>
+      </c>
+      <c r="K4" s="119" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -19836,22 +20498,22 @@
       <c r="E31" s="14"/>
       <c r="F31" s="14"/>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>114</v>
       </c>

--- a/data/SingleCell_Pipeline_MasterSchema.xlsx
+++ b/data/SingleCell_Pipeline_MasterSchema.xlsx
@@ -2839,7 +2839,7 @@
     <t xml:space="preserve">BSA (powder): ASAP HTO staining = CITE staining (0.28 g = 2% x 14 mL). Same wash procedure as unsort.</t>
   </si>
   <si>
-    <t xml:space="preserve">ASAP HTO staining PBS = CITE staining (14 mL/pool). Same 3x pre + 3x post + resuspend washes as unsort.</t>
+    <t xml:space="preserve">ASAP HTO staining PBS = CITE staining (14 mL/pool). Same 3x pre + 3x post + resuspend washes as unsort. [ADAPTED to SOP: 19 mL/pool/modality (was 14).]</t>
   </si>
   <si>
     <t xml:space="preserve">16% Formaldehyde</t>
@@ -4442,7 +4442,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="H6" s="7" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$N$2:$N$102,Pre_GEM_Consumables!$E$2:$E$102,G6)+SUMIFS(Post_GEM_Consumables!$N$2:$N$97,Post_GEM_Consumables!$E$2:$E$97,G6)</f>
-        <v>811.27079</v>
+        <v>819.26207</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6675,7 +6675,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="97" t="n">
-        <v>0.28</v>
+        <v>0.38</v>
       </c>
       <c r="G21" s="96" t="s">
         <v>404</v>
@@ -6690,11 +6690,11 @@
       </c>
       <c r="J21" s="100" t="n">
         <f aca="false">F21*I21*(1+H21)</f>
-        <v>1.848</v>
+        <v>2.508</v>
       </c>
       <c r="K21" s="101" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(G21,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J21,0),ROUND(J21,2))</f>
-        <v>1.85</v>
+        <v>2.51</v>
       </c>
       <c r="L21" s="91" t="n">
         <f aca="false">IFERROR(IF(OR(D21="",P21="",Q21="",Q21=0),"",IF(VLOOKUP(R21,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G21,Unit_Conversions!$A$5:$C$28,3,FALSE()),P21*VLOOKUP(G21,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q21*VLOOKUP(R21,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
@@ -6702,11 +6702,11 @@
       </c>
       <c r="M21" s="92" t="n">
         <f aca="false">IFERROR(F21*L21,"")</f>
-        <v>1.16256</v>
+        <v>1.57776</v>
       </c>
       <c r="N21" s="93" t="n">
         <f aca="false">IFERROR(J21*L21,"")</f>
-        <v>7.672896</v>
+        <v>10.413216</v>
       </c>
       <c r="O21" s="102" t="s">
         <v>922</v>
@@ -6741,7 +6741,7 @@
         <v>11</v>
       </c>
       <c r="F22" s="97" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G22" s="96" t="s">
         <v>337</v>
@@ -6756,11 +6756,11 @@
       </c>
       <c r="J22" s="100" t="n">
         <f aca="false">F22*I22*(1+H22)</f>
-        <v>92.4</v>
+        <v>125.4</v>
       </c>
       <c r="K22" s="101" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(G22,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J22,0),ROUND(J22,2))</f>
-        <v>92.4</v>
+        <v>125.4</v>
       </c>
       <c r="L22" s="91" t="n">
         <f aca="false">IFERROR(IF(OR(D22="",P22="",Q22="",Q22=0),"",IF(VLOOKUP(R22,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G22,Unit_Conversions!$A$5:$C$28,3,FALSE()),P22*VLOOKUP(G22,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q22*VLOOKUP(R22,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
@@ -6768,11 +6768,11 @@
       </c>
       <c r="M22" s="92" t="n">
         <f aca="false">IFERROR(F22*L22,"")</f>
-        <v>0.53256</v>
+        <v>0.72276</v>
       </c>
       <c r="N22" s="93" t="n">
         <f aca="false">IFERROR(J22*L22,"")</f>
-        <v>3.514896</v>
+        <v>4.770216</v>
       </c>
       <c r="O22" s="102"/>
       <c r="P22" s="1" t="n">
@@ -7709,7 +7709,7 @@
         <v>11</v>
       </c>
       <c r="F39" s="86" t="n">
-        <v>0.28</v>
+        <v>0.38</v>
       </c>
       <c r="G39" s="85" t="s">
         <v>404</v>
@@ -7724,11 +7724,11 @@
       </c>
       <c r="J39" s="89" t="n">
         <f aca="false">F39*I39*(1+H39)</f>
-        <v>1.848</v>
+        <v>2.508</v>
       </c>
       <c r="K39" s="90" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(G39,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J39,0),ROUND(J39,2))</f>
-        <v>1.85</v>
+        <v>2.51</v>
       </c>
       <c r="L39" s="91" t="n">
         <f aca="false">IFERROR(IF(OR(D39="",P39="",Q39="",Q39=0),"",IF(VLOOKUP(R39,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G39,Unit_Conversions!$A$5:$C$28,3,FALSE()),P39*VLOOKUP(G39,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q39*VLOOKUP(R39,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
@@ -7736,11 +7736,11 @@
       </c>
       <c r="M39" s="92" t="n">
         <f aca="false">IFERROR(F39*L39,"")</f>
-        <v>1.16256</v>
+        <v>1.57776</v>
       </c>
       <c r="N39" s="93" t="n">
         <f aca="false">IFERROR(J39*L39,"")</f>
-        <v>7.672896</v>
+        <v>10.413216</v>
       </c>
       <c r="O39" s="94" t="s">
         <v>931</v>
@@ -7775,7 +7775,7 @@
         <v>11</v>
       </c>
       <c r="F40" s="86" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G40" s="85" t="s">
         <v>337</v>
@@ -7790,11 +7790,11 @@
       </c>
       <c r="J40" s="89" t="n">
         <f aca="false">F40*I40*(1+H40)</f>
-        <v>92.4</v>
+        <v>125.4</v>
       </c>
       <c r="K40" s="90" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(G40,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J40,0),ROUND(J40,2))</f>
-        <v>92.4</v>
+        <v>125.4</v>
       </c>
       <c r="L40" s="91" t="n">
         <f aca="false">IFERROR(IF(OR(D40="",P40="",Q40="",Q40=0),"",IF(VLOOKUP(R40,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G40,Unit_Conversions!$A$5:$C$28,3,FALSE()),P40*VLOOKUP(G40,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q40*VLOOKUP(R40,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
@@ -7802,11 +7802,11 @@
       </c>
       <c r="M40" s="92" t="n">
         <f aca="false">IFERROR(F40*L40,"")</f>
-        <v>0.53256</v>
+        <v>0.72276</v>
       </c>
       <c r="N40" s="93" t="n">
         <f aca="false">IFERROR(J40*L40,"")</f>
-        <v>3.514896</v>
+        <v>4.770216</v>
       </c>
       <c r="O40" s="94" t="s">
         <v>932</v>
@@ -17865,15 +17865,15 @@
       </c>
       <c r="D23" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A23,Pre_GEM_Consumables!$G$2:$G$110,C23,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A23,Post_GEM_Consumables!$G$2:$G$97,C23,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
-        <v>246.895</v>
+        <v>312.895</v>
       </c>
       <c r="E23" s="108" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(C23,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(D23,0),ROUND(D23,2))</f>
-        <v>246.9</v>
+        <v>312.9</v>
       </c>
       <c r="F23" s="109" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$N$2:$N$110,Pre_GEM_Consumables!$C$2:$C$110,A23,Pre_GEM_Consumables!$G$2:$G$110,C23)+SUMIFS(Post_GEM_Consumables!$N$2:$N$97,Post_GEM_Consumables!$C$2:$C$97,A23,Post_GEM_Consumables!$G$2:$G$97,C23)</f>
-        <v>9.3918858</v>
+        <v>11.9025258</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18932,7 +18932,7 @@
       </c>
       <c r="F75" s="111" t="n">
         <f aca="false">SUM(F2:F73)</f>
-        <v>32478.0547279393</v>
+        <v>32480.5653679393</v>
       </c>
     </row>
   </sheetData>
@@ -19733,29 +19733,29 @@
   <dimension ref="A1:K34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="24"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="118" t="s">
         <v>1066</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>1067</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="119" t="s">
         <v>322</v>
       </c>
@@ -19790,153 +19790,153 @@
         <v>331</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>1068</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>1069</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>1070</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>1071</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>1072</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>1073</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>1074</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>1076</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>1077</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>1078</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>1079</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>1080</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>1081</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>1082</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>1083</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>1084</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>1085</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>1086</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>1087</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
         <v>1088</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>1089</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>1090</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>1091</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
         <v>1092</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
         <v>1093</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
         <v>1094</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
         <v>1095</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
         <v>1096</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
         <v>1097</v>
       </c>
     </row>
@@ -19959,29 +19959,29 @@
   <dimension ref="A1:K34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="24"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="118" t="s">
         <v>1098</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>1099</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="119" t="s">
         <v>322</v>
       </c>
@@ -20016,153 +20016,153 @@
         <v>331</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>1100</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>1101</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>1102</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>1103</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>1104</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>1105</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>1106</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>1107</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>1108</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>1109</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>1110</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>1111</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>1112</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>1113</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>1114</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>1115</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>1116</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>1117</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>1118</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>1119</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
         <v>1120</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>1121</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>1122</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>1123</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
         <v>1124</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
         <v>1125</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
         <v>1126</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
         <v>1128</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
         <v>1129</v>
       </c>
     </row>

--- a/data/SingleCell_Pipeline_MasterSchema.xlsx
+++ b/data/SingleCell_Pipeline_MasterSchema.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2893" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2893" uniqueCount="1129">
   <si>
     <t xml:space="preserve">Experiment inputs</t>
   </si>
@@ -2765,9 +2765,6 @@
   </si>
   <si>
     <t xml:space="preserve">RPMI (mL)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per buffer volume (RPMI-DNase media)</t>
   </si>
   <si>
     <t xml:space="preserve">RPMI base for both media: thaw (J2) + low (J3). 1 mL RPMI per mL media.</t>
@@ -4865,7 +4862,7 @@
       </c>
       <c r="H5" s="7" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$N$2:$N$102,Pre_GEM_Consumables!$E$2:$E$102,G5)+SUMIFS(Post_GEM_Consumables!$N$2:$N$97,Post_GEM_Consumables!$E$2:$E$97,G5)</f>
-        <v>1897.236</v>
+        <v>2205.131808</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5804,9 +5801,11 @@
         <v>473</v>
       </c>
       <c r="E7" s="85" t="s">
-        <v>908</v>
-      </c>
-      <c r="F7" s="86"/>
+        <v>9</v>
+      </c>
+      <c r="F7" s="86" t="n">
+        <v>13.2</v>
+      </c>
       <c r="G7" s="85" t="s">
         <v>337</v>
       </c>
@@ -5814,7 +5813,10 @@
         <f aca="false">Inputs!$B$20</f>
         <v>0.1</v>
       </c>
-      <c r="I7" s="88"/>
+      <c r="I7" s="88" t="n">
+        <f aca="false">VLOOKUP(E7,Inputs!$D$5:$E$23,2,FALSE())</f>
+        <v>54</v>
+      </c>
       <c r="J7" s="89" t="n">
         <f aca="false">J2+J3</f>
         <v>877.8</v>
@@ -5829,14 +5831,14 @@
       </c>
       <c r="M7" s="92" t="n">
         <f aca="false">IFERROR(F7*L7,"")</f>
-        <v>0</v>
+        <v>0.178992</v>
       </c>
       <c r="N7" s="93" t="n">
         <f aca="false">IFERROR(J7*L7,"")</f>
         <v>11.902968</v>
       </c>
       <c r="O7" s="94" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="P7" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D7,1)="K",VLOOKUP(D7,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D7,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -5868,7 +5870,7 @@
         <v>9</v>
       </c>
       <c r="F8" s="86" t="n">
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="G8" s="85" t="s">
         <v>337</v>
@@ -5883,11 +5885,11 @@
       </c>
       <c r="J8" s="89" t="n">
         <f aca="false">F8*I8*(1+H8)</f>
-        <v>7.128</v>
+        <v>17.82</v>
       </c>
       <c r="K8" s="90" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(G8,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J8,0),ROUND(J8,2))</f>
-        <v>7.13</v>
+        <v>17.82</v>
       </c>
       <c r="L8" s="91" t="n">
         <f aca="false">IFERROR(IF(OR(D8="",P8="",Q8="",Q8=0),"",IF(VLOOKUP(R8,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G8,Unit_Conversions!$A$5:$C$28,3,FALSE()),P8*VLOOKUP(G8,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q8*VLOOKUP(R8,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
@@ -5895,11 +5897,11 @@
       </c>
       <c r="M8" s="92" t="n">
         <f aca="false">IFERROR(F8*L8,"")</f>
-        <v>0.0384</v>
+        <v>0.096</v>
       </c>
       <c r="N8" s="93" t="n">
         <f aca="false">IFERROR(J8*L8,"")</f>
-        <v>2.28096</v>
+        <v>5.7024</v>
       </c>
       <c r="O8" s="94"/>
       <c r="P8" s="1" t="n">
@@ -5923,15 +5925,17 @@
         <v>901</v>
       </c>
       <c r="C9" s="85" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D9" s="85" t="s">
         <v>483</v>
       </c>
       <c r="E9" s="85" t="s">
-        <v>908</v>
-      </c>
-      <c r="F9" s="95"/>
+        <v>9</v>
+      </c>
+      <c r="F9" s="95" t="n">
+        <v>1.05</v>
+      </c>
       <c r="G9" s="85" t="s">
         <v>488</v>
       </c>
@@ -5939,7 +5943,10 @@
         <f aca="false">Inputs!$B$20</f>
         <v>0.1</v>
       </c>
-      <c r="I9" s="88"/>
+      <c r="I9" s="88" t="n">
+        <f aca="false">VLOOKUP(E9,Inputs!$D$5:$E$23,2,FALSE())</f>
+        <v>54</v>
+      </c>
       <c r="J9" s="89" t="n">
         <f aca="false">J2*0.1+J3*0.025</f>
         <v>75.405</v>
@@ -5961,7 +5968,7 @@
         <v>292.5714</v>
       </c>
       <c r="O9" s="94" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="P9" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D9,1)="K",VLOOKUP(D9,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D9,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -6050,7 +6057,7 @@
         <v>901</v>
       </c>
       <c r="C11" s="85" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D11" s="85" t="s">
         <v>555</v>
@@ -6116,7 +6123,7 @@
         <v>901</v>
       </c>
       <c r="C12" s="85" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D12" s="85" t="s">
         <v>555</v>
@@ -6182,7 +6189,7 @@
         <v>901</v>
       </c>
       <c r="C13" s="85" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D13" s="85"/>
       <c r="E13" s="85" t="s">
@@ -6192,7 +6199,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="85" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H13" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -6223,7 +6230,7 @@
         <v/>
       </c>
       <c r="O13" s="94" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="P13" s="1" t="str">
         <f aca="false">IFERROR(IF(LEFT(D13,1)="K",VLOOKUP(D13,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D13,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -6240,13 +6247,13 @@
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="77" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B14" s="77" t="s">
         <v>896</v>
       </c>
       <c r="C14" s="78" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D14" s="77"/>
       <c r="E14" s="77" t="s">
@@ -6272,13 +6279,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="96" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B15" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C15" s="96" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D15" s="96" t="s">
         <v>551</v>
@@ -6336,13 +6343,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="96" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B16" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C16" s="96" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D16" s="96" t="s">
         <v>555</v>
@@ -6402,7 +6409,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="96" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B17" s="96" t="s">
         <v>901</v>
@@ -6466,13 +6473,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="96" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B18" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C18" s="96" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D18" s="96" t="s">
         <v>584</v>
@@ -6532,13 +6539,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="96" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B19" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C19" s="96" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D19" s="96" t="s">
         <v>428</v>
@@ -6596,13 +6603,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="96" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B20" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C20" s="96" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D20" s="96" t="s">
         <v>431</v>
@@ -6660,7 +6667,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="96" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B21" s="96" t="s">
         <v>901</v>
@@ -6709,7 +6716,7 @@
         <v>10.413216</v>
       </c>
       <c r="O21" s="102" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="P21" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D21,1)="K",VLOOKUP(D21,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D21,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -6726,13 +6733,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="96" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B22" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C22" s="96" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D22" s="96" t="s">
         <v>339</v>
@@ -6790,13 +6797,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="96" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B23" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C23" s="96" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D23" s="96" t="s">
         <v>421</v>
@@ -6854,13 +6861,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="96" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B24" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C24" s="96" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D24" s="96" t="s">
         <v>339</v>
@@ -6918,7 +6925,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="96" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B25" s="96" t="s">
         <v>901</v>
@@ -6967,7 +6974,7 @@
         <v>0.822096</v>
       </c>
       <c r="O25" s="102" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="P25" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D25,1)="K",VLOOKUP(D25,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D25,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -6984,13 +6991,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="96" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B26" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C26" s="96" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D26" s="96" t="s">
         <v>551</v>
@@ -7048,13 +7055,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="96" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B27" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C27" s="96" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D27" s="96" t="s">
         <v>555</v>
@@ -7114,7 +7121,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="96" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B28" s="96" t="s">
         <v>901</v>
@@ -7178,13 +7185,13 @@
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="77" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B29" s="77" t="s">
         <v>896</v>
       </c>
       <c r="C29" s="78" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D29" s="77"/>
       <c r="E29" s="77" t="s">
@@ -7210,13 +7217,13 @@
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="77" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B30" s="77" t="s">
         <v>896</v>
       </c>
       <c r="C30" s="78" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D30" s="77"/>
       <c r="E30" s="77" t="s">
@@ -7242,13 +7249,13 @@
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="77" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B31" s="77" t="s">
         <v>896</v>
       </c>
       <c r="C31" s="78" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D31" s="77"/>
       <c r="E31" s="77" t="s">
@@ -7274,13 +7281,13 @@
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="77" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B32" s="77" t="s">
         <v>896</v>
       </c>
       <c r="C32" s="78" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D32" s="77"/>
       <c r="E32" s="77" t="s">
@@ -7306,13 +7313,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B33" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C33" s="85" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D33" s="85" t="s">
         <v>551</v>
@@ -7370,13 +7377,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B34" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C34" s="85" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D34" s="85" t="s">
         <v>555</v>
@@ -7436,7 +7443,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B35" s="85" t="s">
         <v>901</v>
@@ -7500,13 +7507,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B36" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C36" s="85" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D36" s="85" t="s">
         <v>584</v>
@@ -7566,13 +7573,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B37" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C37" s="85" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D37" s="85" t="s">
         <v>424</v>
@@ -7630,13 +7637,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B38" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C38" s="85" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D38" s="85" t="s">
         <v>431</v>
@@ -7694,7 +7701,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B39" s="85" t="s">
         <v>901</v>
@@ -7743,7 +7750,7 @@
         <v>10.413216</v>
       </c>
       <c r="O39" s="94" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="P39" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D39,1)="K",VLOOKUP(D39,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D39,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -7760,13 +7767,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B40" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C40" s="85" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D40" s="85" t="s">
         <v>339</v>
@@ -7809,7 +7816,7 @@
         <v>4.770216</v>
       </c>
       <c r="O40" s="94" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="P40" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D40,1)="K",VLOOKUP(D40,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D40,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -7826,13 +7833,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B41" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C41" s="85" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D41" s="85" t="s">
         <v>393</v>
@@ -7890,7 +7897,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B42" s="85" t="s">
         <v>901</v>
@@ -7954,13 +7961,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B43" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C43" s="85" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D43" s="85" t="s">
         <v>438</v>
@@ -8018,7 +8025,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B44" s="85" t="s">
         <v>901</v>
@@ -8082,7 +8089,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B45" s="85" t="s">
         <v>901</v>
@@ -8146,13 +8153,13 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B46" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C46" s="85" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D46" s="85" t="s">
         <v>455</v>
@@ -8210,7 +8217,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B47" s="85" t="s">
         <v>901</v>
@@ -8274,7 +8281,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B48" s="85" t="s">
         <v>901</v>
@@ -8338,7 +8345,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B49" s="85" t="s">
         <v>901</v>
@@ -8404,13 +8411,13 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B50" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C50" s="85" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D50" s="85" t="s">
         <v>413</v>
@@ -8468,13 +8475,13 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B51" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C51" s="85" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D51" s="85" t="s">
         <v>339</v>
@@ -8532,7 +8539,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B52" s="85" t="s">
         <v>901</v>
@@ -8598,7 +8605,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B53" s="85" t="s">
         <v>901</v>
@@ -8647,7 +8654,7 @@
         <v>0.822096</v>
       </c>
       <c r="O53" s="94" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="P53" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D53,1)="K",VLOOKUP(D53,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D53,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -8664,13 +8671,13 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B54" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C54" s="85" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D54" s="85" t="s">
         <v>551</v>
@@ -8728,13 +8735,13 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B55" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C55" s="85" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D55" s="85" t="s">
         <v>555</v>
@@ -8794,13 +8801,13 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B56" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C56" s="85" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D56" s="85" t="s">
         <v>557</v>
@@ -8858,7 +8865,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="85" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B57" s="85" t="s">
         <v>901</v>
@@ -8922,13 +8929,13 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="85" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B58" s="85" t="s">
         <v>896</v>
       </c>
       <c r="C58" s="85" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D58" s="85"/>
       <c r="E58" s="85" t="s">
@@ -8954,13 +8961,13 @@
     </row>
     <row r="59" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="77" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B59" s="77" t="s">
         <v>896</v>
       </c>
       <c r="C59" s="78" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="D59" s="77"/>
       <c r="E59" s="77" t="s">
@@ -8986,13 +8993,13 @@
     </row>
     <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="77" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B60" s="77" t="s">
         <v>901</v>
       </c>
       <c r="C60" s="78" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D60" s="77" t="s">
         <v>584</v>
@@ -9052,7 +9059,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="96" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B61" s="96" t="s">
         <v>901</v>
@@ -9101,7 +9108,7 @@
         <v/>
       </c>
       <c r="O61" s="102" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="P61" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D61,1)="K",VLOOKUP(D61,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D61,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -9118,13 +9125,13 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="96" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B62" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C62" s="96" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D62" s="96" t="s">
         <v>431</v>
@@ -9167,7 +9174,7 @@
         <v>15.114</v>
       </c>
       <c r="O62" s="102" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="P62" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D62,1)="K",VLOOKUP(D62,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D62,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -9184,7 +9191,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="96" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B63" s="96" t="s">
         <v>901</v>
@@ -9248,13 +9255,13 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="96" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B64" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C64" s="96" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D64" s="96" t="s">
         <v>339</v>
@@ -9297,7 +9304,7 @@
         <v>1.506384</v>
       </c>
       <c r="O64" s="102" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="P64" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D64,1)="K",VLOOKUP(D64,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D64,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -9314,13 +9321,13 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="96" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B65" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C65" s="96" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="D65" s="96"/>
       <c r="E65" s="96" t="s">
@@ -9361,7 +9368,7 @@
         <v/>
       </c>
       <c r="O65" s="102" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="P65" s="1" t="str">
         <f aca="false">IFERROR(IF(LEFT(D65,1)="K",VLOOKUP(D65,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D65,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -9378,13 +9385,13 @@
     </row>
     <row r="66" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="96" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B66" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C66" s="96" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="D66" s="96" t="s">
         <v>604</v>
@@ -9427,7 +9434,7 @@
         <v/>
       </c>
       <c r="O66" s="102" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="P66" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D66,1)="K",VLOOKUP(D66,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D66,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -9444,7 +9451,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="96" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B67" s="96" t="s">
         <v>901</v>
@@ -9493,7 +9500,7 @@
         <v/>
       </c>
       <c r="O67" s="102" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="P67" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D67,1)="K",VLOOKUP(D67,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D67,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -9510,13 +9517,13 @@
     </row>
     <row r="68" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="96" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B68" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C68" s="96" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D68" s="96"/>
       <c r="E68" s="96" t="s">
@@ -9557,7 +9564,7 @@
         <v/>
       </c>
       <c r="O68" s="102" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="P68" s="1" t="str">
         <f aca="false">IFERROR(IF(LEFT(D68,1)="K",VLOOKUP(D68,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D68,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -9574,13 +9581,13 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="96" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B69" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C69" s="96" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="D69" s="96" t="s">
         <v>584</v>
@@ -9623,7 +9630,7 @@
         <v/>
       </c>
       <c r="O69" s="102" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="P69" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D69,1)="K",VLOOKUP(D69,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D69,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -9640,13 +9647,13 @@
     </row>
     <row r="70" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="96" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B70" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C70" s="96" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="D70" s="96" t="s">
         <v>625</v>
@@ -9689,7 +9696,7 @@
         <v>10.538</v>
       </c>
       <c r="O70" s="102" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="P70" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D70,1)="K",VLOOKUP(D70,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D70,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -9706,13 +9713,13 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="96" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B71" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C71" s="96" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="D71" s="96" t="s">
         <v>544</v>
@@ -9770,7 +9777,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="85" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B72" s="85" t="s">
         <v>901</v>
@@ -9836,13 +9843,13 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="85" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B73" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C73" s="85" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="D73" s="85" t="s">
         <v>510</v>
@@ -9900,13 +9907,13 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="85" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B74" s="85" t="s">
         <v>896</v>
       </c>
       <c r="C74" s="85" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D74" s="85"/>
       <c r="E74" s="85" t="s">
@@ -9927,18 +9934,18 @@
       <c r="M74" s="92"/>
       <c r="N74" s="93"/>
       <c r="O74" s="94" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="85" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B75" s="85" t="s">
         <v>896</v>
       </c>
       <c r="C75" s="85" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D75" s="85"/>
       <c r="E75" s="85" t="s">
@@ -9959,18 +9966,18 @@
       <c r="M75" s="105"/>
       <c r="N75" s="106"/>
       <c r="O75" s="94" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="85" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B76" s="85" t="s">
         <v>896</v>
       </c>
       <c r="C76" s="85" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="D76" s="85"/>
       <c r="E76" s="85" t="s">
@@ -9991,18 +9998,18 @@
       <c r="M76" s="105"/>
       <c r="N76" s="106"/>
       <c r="O76" s="94" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="85" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B77" s="85" t="s">
         <v>896</v>
       </c>
       <c r="C77" s="85" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D77" s="85"/>
       <c r="E77" s="85" t="s">
@@ -10023,18 +10030,18 @@
       <c r="M77" s="105"/>
       <c r="N77" s="106"/>
       <c r="O77" s="94" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="85" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B78" s="85" t="s">
         <v>896</v>
       </c>
       <c r="C78" s="85" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="D78" s="85"/>
       <c r="E78" s="85" t="s">
@@ -10055,12 +10062,12 @@
       <c r="M78" s="105"/>
       <c r="N78" s="106"/>
       <c r="O78" s="94" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="85" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B79" s="85" t="s">
         <v>901</v>
@@ -10109,7 +10116,7 @@
         <v>0</v>
       </c>
       <c r="O79" s="94" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="P79" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D79,1)="K",VLOOKUP(D79,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D79,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -10126,13 +10133,13 @@
     </row>
     <row r="80" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="85" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B80" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C80" s="85" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="D80" s="85" t="s">
         <v>288</v>
@@ -10175,7 +10182,7 @@
         <v>0</v>
       </c>
       <c r="O80" s="94" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="P80" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D80,1)="K",VLOOKUP(D80,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D80,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -10192,7 +10199,7 @@
     </row>
     <row r="81" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="85" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B81" s="85" t="s">
         <v>901</v>
@@ -10210,7 +10217,7 @@
         <v>1</v>
       </c>
       <c r="G81" s="85" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H81" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -10241,7 +10248,7 @@
         <v>0</v>
       </c>
       <c r="O81" s="94" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="P81" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D81,1)="K",VLOOKUP(D81,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D81,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -10258,7 +10265,7 @@
     </row>
     <row r="82" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="85" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B82" s="85" t="s">
         <v>901</v>
@@ -10276,7 +10283,7 @@
         <v>1</v>
       </c>
       <c r="G82" s="85" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H82" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -10307,7 +10314,7 @@
         <v/>
       </c>
       <c r="O82" s="94" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="P82" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D82,1)="K",VLOOKUP(D82,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D82,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -10324,13 +10331,13 @@
     </row>
     <row r="83" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="85" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B83" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C83" s="85" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D83" s="85" t="s">
         <v>517</v>
@@ -10373,7 +10380,7 @@
         <v>0</v>
       </c>
       <c r="O83" s="94" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="P83" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D83,1)="K",VLOOKUP(D83,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D83,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -10390,13 +10397,13 @@
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="85" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B84" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C84" s="85" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="D84" s="85" t="s">
         <v>333</v>
@@ -10439,7 +10446,7 @@
         <v>0</v>
       </c>
       <c r="O84" s="94" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="P84" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D84,1)="K",VLOOKUP(D84,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D84,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -10456,13 +10463,13 @@
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="85" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B85" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C85" s="85" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="D85" s="85" t="s">
         <v>523</v>
@@ -10505,7 +10512,7 @@
         <v>0</v>
       </c>
       <c r="O85" s="94" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P85" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D85,1)="K",VLOOKUP(D85,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D85,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -10522,7 +10529,7 @@
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="85" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B86" s="85" t="s">
         <v>901</v>
@@ -10571,7 +10578,7 @@
         <v>0</v>
       </c>
       <c r="O86" s="94" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="P86" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D86,1)="K",VLOOKUP(D86,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D86,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -10588,7 +10595,7 @@
     </row>
     <row r="87" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="85" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B87" s="85" t="s">
         <v>901</v>
@@ -10637,7 +10644,7 @@
         <v>0</v>
       </c>
       <c r="O87" s="94" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="P87" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D87,1)="K",VLOOKUP(D87,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D87,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -10654,13 +10661,13 @@
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="85" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B88" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C88" s="85" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="D88" s="85" t="s">
         <v>536</v>
@@ -10703,7 +10710,7 @@
         <v>0</v>
       </c>
       <c r="O88" s="94" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="P88" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D88,1)="K",VLOOKUP(D88,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D88,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -10958,13 +10965,13 @@
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>901</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>428</v>
@@ -11007,7 +11014,7 @@
         <v>853.05</v>
       </c>
       <c r="O103" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="P103" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D103,1)="K",VLOOKUP(D103,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D103,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11024,7 +11031,7 @@
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>901</v>
@@ -11073,7 +11080,7 @@
         <v>1.096128</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="P104" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D104,1)="K",VLOOKUP(D104,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D104,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11090,13 +11097,13 @@
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>901</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>339</v>
@@ -11139,7 +11146,7 @@
         <v>0.376596</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="P105" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D105,1)="K",VLOOKUP(D105,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D105,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11250,7 +11257,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="85" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B2" s="85" t="s">
         <v>901</v>
@@ -11268,7 +11275,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="85" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -11299,7 +11306,7 @@
         <v>13018.5</v>
       </c>
       <c r="O2" s="94" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="P2" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D2,1)="K",VLOOKUP(D2,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D2,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11316,7 +11323,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="85" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B3" s="85" t="s">
         <v>901</v>
@@ -11334,7 +11341,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="85" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H3" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -11365,7 +11372,7 @@
         <v>687.5</v>
       </c>
       <c r="O3" s="94" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="P3" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D3,1)="K",VLOOKUP(D3,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D3,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11382,7 +11389,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="85" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B4" s="85" t="s">
         <v>901</v>
@@ -11431,7 +11438,7 @@
         <v>0.31440992</v>
       </c>
       <c r="O4" s="94" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P4" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D4,1)="K",VLOOKUP(D4,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D4,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11448,13 +11455,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="85" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B5" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C5" s="85" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D5" s="85" t="s">
         <v>346</v>
@@ -11497,7 +11504,7 @@
         <v>2.49392</v>
       </c>
       <c r="O5" s="94" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P5" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D5,1)="K",VLOOKUP(D5,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D5,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11514,13 +11521,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="85" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B6" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C6" s="85" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D6" s="85" t="s">
         <v>360</v>
@@ -11563,7 +11570,7 @@
         <v>31.19116</v>
       </c>
       <c r="O6" s="94" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P6" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D6,1)="K",VLOOKUP(D6,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D6,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11580,13 +11587,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="85" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B7" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C7" s="85" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D7" s="85" t="s">
         <v>557</v>
@@ -11629,7 +11636,7 @@
         <v>0.85844</v>
       </c>
       <c r="O7" s="94" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="P7" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D7,1)="K",VLOOKUP(D7,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D7,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11646,13 +11653,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="85" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B8" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C8" s="85" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D8" s="85" t="s">
         <v>529</v>
@@ -11695,7 +11702,7 @@
         <v>0.267609375</v>
       </c>
       <c r="O8" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P8" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D8,1)="K",VLOOKUP(D8,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D8,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11712,13 +11719,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="85" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B9" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C9" s="85" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D9" s="85" t="s">
         <v>536</v>
@@ -11761,7 +11768,7 @@
         <v>0.330733333333333</v>
       </c>
       <c r="O9" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P9" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D9,1)="K",VLOOKUP(D9,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D9,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11778,13 +11785,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="85" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B10" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C10" s="85" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D10" s="85" t="s">
         <v>540</v>
@@ -11827,7 +11834,7 @@
         <v>0.330733333333333</v>
       </c>
       <c r="O10" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P10" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D10,1)="K",VLOOKUP(D10,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D10,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11844,13 +11851,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="85" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B11" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C11" s="85" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D11" s="85" t="s">
         <v>544</v>
@@ -11893,7 +11900,7 @@
         <v>1.580128</v>
       </c>
       <c r="O11" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P11" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D11,1)="K",VLOOKUP(D11,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D11,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11910,7 +11917,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="85" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B12" s="85" t="s">
         <v>901</v>
@@ -11959,7 +11966,7 @@
         <v>0.00121968</v>
       </c>
       <c r="O12" s="94" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="P12" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D12,1)="K",VLOOKUP(D12,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D12,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11976,13 +11983,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="85" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B13" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C13" s="85" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D13" s="85"/>
       <c r="E13" s="85" t="s">
@@ -12023,7 +12030,7 @@
         <v/>
       </c>
       <c r="O13" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P13" s="1" t="str">
         <f aca="false">IFERROR(IF(LEFT(D13,1)="K",VLOOKUP(D13,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D13,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12040,7 +12047,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="96" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B14" s="96" t="s">
         <v>901</v>
@@ -12058,7 +12065,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="96" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H14" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -12089,7 +12096,7 @@
         <v>3437.5</v>
       </c>
       <c r="O14" s="102" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="P14" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D14,1)="K",VLOOKUP(D14,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D14,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12106,7 +12113,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="96" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B15" s="96" t="s">
         <v>901</v>
@@ -12124,7 +12131,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="96" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H15" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -12155,7 +12162,7 @@
         <v>82.5</v>
       </c>
       <c r="O15" s="102" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="P15" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D15,1)="K",VLOOKUP(D15,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D15,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12172,7 +12179,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="96" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B16" s="96" t="s">
         <v>901</v>
@@ -12190,7 +12197,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="96" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H16" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -12221,7 +12228,7 @@
         <v>22</v>
       </c>
       <c r="O16" s="102" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="P16" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D16,1)="K",VLOOKUP(D16,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D16,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12238,7 +12245,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="85" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B17" s="85" t="s">
         <v>901</v>
@@ -12256,7 +12263,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="85" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H17" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -12287,7 +12294,7 @@
         <v>687.5</v>
       </c>
       <c r="O17" s="94" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="P17" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D17,1)="K",VLOOKUP(D17,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D17,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12304,7 +12311,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="85" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B18" s="85" t="s">
         <v>901</v>
@@ -12322,7 +12329,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="85" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H18" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -12353,7 +12360,7 @@
         <v>88</v>
       </c>
       <c r="O18" s="94" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="P18" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D18,1)="K",VLOOKUP(D18,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D18,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12370,7 +12377,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="85" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B19" s="85" t="s">
         <v>901</v>
@@ -12419,7 +12426,7 @@
         <v>0.24854192</v>
       </c>
       <c r="O19" s="94" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P19" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D19,1)="K",VLOOKUP(D19,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D19,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12436,13 +12443,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="85" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B20" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C20" s="85" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D20" s="85" t="s">
         <v>346</v>
@@ -12485,7 +12492,7 @@
         <v>2.01432</v>
       </c>
       <c r="O20" s="94" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P20" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D20,1)="K",VLOOKUP(D20,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D20,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12502,13 +12509,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="85" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B21" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C21" s="85" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D21" s="85" t="s">
         <v>360</v>
@@ -12551,7 +12558,7 @@
         <v>47.9864</v>
       </c>
       <c r="O21" s="94" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P21" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D21,1)="K",VLOOKUP(D21,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D21,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12568,13 +12575,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="85" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B22" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C22" s="85" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D22" s="85" t="s">
         <v>375</v>
@@ -12586,7 +12593,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="85" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H22" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -12617,7 +12624,7 @@
         <v/>
       </c>
       <c r="O22" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P22" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D22,1)="K",VLOOKUP(D22,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D22,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12634,13 +12641,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="85" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B23" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C23" s="85" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="D23" s="85" t="s">
         <v>367</v>
@@ -12652,7 +12659,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="85" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H23" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -12683,7 +12690,7 @@
         <v>7.50904</v>
       </c>
       <c r="O23" s="94" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P23" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D23,1)="K",VLOOKUP(D23,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D23,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12700,13 +12707,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="85" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B24" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C24" s="85" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="D24" s="85" t="s">
         <v>579</v>
@@ -12749,7 +12756,7 @@
         <v>2.376</v>
       </c>
       <c r="O24" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P24" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D24,1)="K",VLOOKUP(D24,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D24,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12766,13 +12773,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="85" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B25" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C25" s="85" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D25" s="85" t="s">
         <v>557</v>
@@ -12815,7 +12822,7 @@
         <v>0.85844</v>
       </c>
       <c r="O25" s="94" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="P25" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D25,1)="K",VLOOKUP(D25,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D25,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12832,13 +12839,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="85" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B26" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C26" s="85" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D26" s="85" t="s">
         <v>536</v>
@@ -12881,7 +12888,7 @@
         <v>0.661466666666667</v>
       </c>
       <c r="O26" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P26" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D26,1)="K",VLOOKUP(D26,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D26,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12898,13 +12905,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="85" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B27" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C27" s="85" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D27" s="85" t="s">
         <v>540</v>
@@ -12947,7 +12954,7 @@
         <v>0.165366666666667</v>
       </c>
       <c r="O27" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P27" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D27,1)="K",VLOOKUP(D27,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D27,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12964,13 +12971,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="85" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B28" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C28" s="85" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D28" s="85" t="s">
         <v>544</v>
@@ -13013,7 +13020,7 @@
         <v>1.580128</v>
       </c>
       <c r="O28" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P28" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D28,1)="K",VLOOKUP(D28,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D28,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13030,13 +13037,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="85" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B29" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C29" s="85" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="D29" s="85" t="s">
         <v>388</v>
@@ -13048,7 +13055,7 @@
         <v>1</v>
       </c>
       <c r="G29" s="85" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H29" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -13079,7 +13086,7 @@
         <v/>
       </c>
       <c r="O29" s="94" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="P29" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D29,1)="K",VLOOKUP(D29,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D29,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13096,7 +13103,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="96" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B30" s="96" t="s">
         <v>901</v>
@@ -13114,7 +13121,7 @@
         <v>1</v>
       </c>
       <c r="G30" s="96" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H30" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -13145,7 +13152,7 @@
         <v>687.5</v>
       </c>
       <c r="O30" s="102" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="P30" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D30,1)="K",VLOOKUP(D30,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D30,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13162,7 +13169,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="96" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B31" s="96" t="s">
         <v>901</v>
@@ -13180,7 +13187,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="96" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H31" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -13211,7 +13218,7 @@
         <v>88</v>
       </c>
       <c r="O31" s="102" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="P31" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D31,1)="K",VLOOKUP(D31,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D31,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13228,7 +13235,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="96" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B32" s="96" t="s">
         <v>901</v>
@@ -13246,7 +13253,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="96" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H32" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -13277,7 +13284,7 @@
         <v>198</v>
       </c>
       <c r="O32" s="102" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="P32" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D32,1)="K",VLOOKUP(D32,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D32,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13294,7 +13301,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="96" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B33" s="96" t="s">
         <v>901</v>
@@ -13312,7 +13319,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="96" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H33" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -13343,7 +13350,7 @@
         <v>198</v>
       </c>
       <c r="O33" s="102" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="P33" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D33,1)="K",VLOOKUP(D33,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D33,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13360,7 +13367,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="96" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B34" s="96" t="s">
         <v>901</v>
@@ -13409,7 +13416,7 @@
         <v>0.29333216</v>
       </c>
       <c r="O34" s="102" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P34" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D34,1)="K",VLOOKUP(D34,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D34,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13426,13 +13433,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="96" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B35" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C35" s="96" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D35" s="96" t="s">
         <v>346</v>
@@ -13475,7 +13482,7 @@
         <v>3.06944</v>
       </c>
       <c r="O35" s="102" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P35" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D35,1)="K",VLOOKUP(D35,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D35,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13492,13 +13499,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="96" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B36" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C36" s="96" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D36" s="96" t="s">
         <v>360</v>
@@ -13541,7 +13548,7 @@
         <v>76.77824</v>
       </c>
       <c r="O36" s="102" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P36" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D36,1)="K",VLOOKUP(D36,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D36,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13558,13 +13565,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="96" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B37" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C37" s="96" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D37" s="96" t="s">
         <v>375</v>
@@ -13576,7 +13583,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="96" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H37" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -13607,7 +13614,7 @@
         <v/>
       </c>
       <c r="O37" s="102" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P37" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D37,1)="K",VLOOKUP(D37,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D37,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13624,13 +13631,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="96" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B38" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C38" s="96" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="D38" s="96" t="s">
         <v>367</v>
@@ -13642,7 +13649,7 @@
         <v>1</v>
       </c>
       <c r="G38" s="96" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H38" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -13673,7 +13680,7 @@
         <v>7.50904</v>
       </c>
       <c r="O38" s="102" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P38" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D38,1)="K",VLOOKUP(D38,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D38,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13690,13 +13697,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="96" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B39" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C39" s="96" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="D39" s="96" t="s">
         <v>579</v>
@@ -13739,7 +13746,7 @@
         <v>2.376</v>
       </c>
       <c r="O39" s="102" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P39" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D39,1)="K",VLOOKUP(D39,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D39,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13756,13 +13763,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="96" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B40" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C40" s="96" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D40" s="96" t="s">
         <v>557</v>
@@ -13805,7 +13812,7 @@
         <v>1.71688</v>
       </c>
       <c r="O40" s="102" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="P40" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D40,1)="K",VLOOKUP(D40,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D40,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13822,13 +13829,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="96" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B41" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C41" s="96" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D41" s="96" t="s">
         <v>536</v>
@@ -13871,7 +13878,7 @@
         <v>0.826833333333333</v>
       </c>
       <c r="O41" s="102" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P41" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D41,1)="K",VLOOKUP(D41,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D41,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13888,13 +13895,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="96" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B42" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C42" s="96" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D42" s="96" t="s">
         <v>540</v>
@@ -13937,7 +13944,7 @@
         <v>0.330733333333333</v>
       </c>
       <c r="O42" s="102" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P42" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D42,1)="K",VLOOKUP(D42,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D42,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13954,13 +13961,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="96" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B43" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C43" s="96" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D43" s="96" t="s">
         <v>544</v>
@@ -14003,7 +14010,7 @@
         <v>1.580128</v>
       </c>
       <c r="O43" s="102" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P43" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D43,1)="K",VLOOKUP(D43,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D43,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14020,13 +14027,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="96" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B44" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C44" s="96" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D44" s="96"/>
       <c r="E44" s="96" t="s">
@@ -14067,7 +14074,7 @@
         <v/>
       </c>
       <c r="O44" s="102" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P44" s="1" t="str">
         <f aca="false">IFERROR(IF(LEFT(D44,1)="K",VLOOKUP(D44,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D44,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14084,13 +14091,13 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="96" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B45" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C45" s="96" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="D45" s="96" t="s">
         <v>388</v>
@@ -14102,7 +14109,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="96" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H45" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -14133,7 +14140,7 @@
         <v/>
       </c>
       <c r="O45" s="102" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="P45" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D45,1)="K",VLOOKUP(D45,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D45,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14150,7 +14157,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="85" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B46" s="85" t="s">
         <v>901</v>
@@ -14168,7 +14175,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="85" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H46" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -14199,7 +14206,7 @@
         <v>368.5</v>
       </c>
       <c r="O46" s="94" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="P46" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D46,1)="K",VLOOKUP(D46,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D46,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14216,7 +14223,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="85" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B47" s="85" t="s">
         <v>901</v>
@@ -14234,7 +14241,7 @@
         <v>1</v>
       </c>
       <c r="G47" s="85" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H47" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -14265,7 +14272,7 @@
         <v>88</v>
       </c>
       <c r="O47" s="94" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="P47" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D47,1)="K",VLOOKUP(D47,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D47,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14282,7 +14289,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="85" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B48" s="85" t="s">
         <v>901</v>
@@ -14331,7 +14338,7 @@
         <v>0.10626704</v>
       </c>
       <c r="O48" s="94" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P48" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D48,1)="K",VLOOKUP(D48,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D48,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14348,13 +14355,13 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="85" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B49" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C49" s="85" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D49" s="85" t="s">
         <v>346</v>
@@ -14397,7 +14404,7 @@
         <v>0.9592</v>
       </c>
       <c r="O49" s="94" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P49" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D49,1)="K",VLOOKUP(D49,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D49,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14414,13 +14421,13 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="85" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B50" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C50" s="85" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D50" s="85" t="s">
         <v>360</v>
@@ -14463,7 +14470,7 @@
         <v>28.79184</v>
       </c>
       <c r="O50" s="94" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P50" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D50,1)="K",VLOOKUP(D50,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D50,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14480,13 +14487,13 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="85" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B51" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C51" s="85" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D51" s="85" t="s">
         <v>375</v>
@@ -14498,7 +14505,7 @@
         <v>1</v>
       </c>
       <c r="G51" s="85" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H51" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -14529,7 +14536,7 @@
         <v/>
       </c>
       <c r="O51" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P51" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D51,1)="K",VLOOKUP(D51,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D51,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14546,13 +14553,13 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="85" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B52" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C52" s="85" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="D52" s="85" t="s">
         <v>367</v>
@@ -14564,7 +14571,7 @@
         <v>1</v>
       </c>
       <c r="G52" s="85" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H52" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -14595,7 +14602,7 @@
         <v>7.50904</v>
       </c>
       <c r="O52" s="94" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P52" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D52,1)="K",VLOOKUP(D52,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D52,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14612,13 +14619,13 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="85" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B53" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C53" s="85" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="D53" s="85" t="s">
         <v>579</v>
@@ -14661,7 +14668,7 @@
         <v>2.376</v>
       </c>
       <c r="O53" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P53" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D53,1)="K",VLOOKUP(D53,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D53,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14678,13 +14685,13 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="85" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B54" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C54" s="85" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D54" s="85" t="s">
         <v>557</v>
@@ -14727,7 +14734,7 @@
         <v>0.85844</v>
       </c>
       <c r="O54" s="94" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="P54" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D54,1)="K",VLOOKUP(D54,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D54,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14744,13 +14751,13 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="85" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B55" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C55" s="85" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D55" s="85" t="s">
         <v>536</v>
@@ -14793,7 +14800,7 @@
         <v>0.4961</v>
       </c>
       <c r="O55" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P55" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D55,1)="K",VLOOKUP(D55,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D55,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14810,13 +14817,13 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="85" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B56" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C56" s="85" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D56" s="85" t="s">
         <v>540</v>
@@ -14859,7 +14866,7 @@
         <v>0.165366666666667</v>
       </c>
       <c r="O56" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P56" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D56,1)="K",VLOOKUP(D56,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D56,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14876,13 +14883,13 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="85" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B57" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C57" s="85" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D57" s="85" t="s">
         <v>544</v>
@@ -14925,7 +14932,7 @@
         <v>1.580128</v>
       </c>
       <c r="O57" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P57" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D57,1)="K",VLOOKUP(D57,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D57,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14942,13 +14949,13 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="85" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B58" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C58" s="85" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="D58" s="85" t="s">
         <v>388</v>
@@ -14960,7 +14967,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="85" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H58" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -14991,7 +14998,7 @@
         <v/>
       </c>
       <c r="O58" s="94" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="P58" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D58,1)="K",VLOOKUP(D58,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D58,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15008,7 +15015,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="96" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B59" s="96" t="s">
         <v>901</v>
@@ -15057,7 +15064,7 @@
         <v>0.04479024</v>
       </c>
       <c r="O59" s="102" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P59" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D59,1)="K",VLOOKUP(D59,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D59,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15074,13 +15081,13 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="96" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B60" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C60" s="96" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D60" s="96" t="s">
         <v>346</v>
@@ -15123,7 +15130,7 @@
         <v>0.52756</v>
       </c>
       <c r="O60" s="102" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P60" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D60,1)="K",VLOOKUP(D60,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D60,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15140,13 +15147,13 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="96" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B61" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C61" s="96" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D61" s="96" t="s">
         <v>360</v>
@@ -15189,7 +15196,7 @@
         <v>20.934067</v>
       </c>
       <c r="O61" s="102" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P61" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D61,1)="K",VLOOKUP(D61,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D61,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15206,13 +15213,13 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="96" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B62" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C62" s="96" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D62" s="96" t="s">
         <v>375</v>
@@ -15224,7 +15231,7 @@
         <v>1</v>
       </c>
       <c r="G62" s="96" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H62" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -15255,7 +15262,7 @@
         <v/>
       </c>
       <c r="O62" s="102" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P62" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D62,1)="K",VLOOKUP(D62,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D62,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15272,13 +15279,13 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="96" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B63" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C63" s="96" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="D63" s="96" t="s">
         <v>367</v>
@@ -15290,7 +15297,7 @@
         <v>1</v>
       </c>
       <c r="G63" s="96" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H63" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -15321,7 +15328,7 @@
         <v>1.87726</v>
       </c>
       <c r="O63" s="102" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P63" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D63,1)="K",VLOOKUP(D63,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D63,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15338,13 +15345,13 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="96" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B64" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C64" s="96" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="D64" s="96" t="s">
         <v>579</v>
@@ -15387,7 +15394,7 @@
         <v>0.594</v>
       </c>
       <c r="O64" s="102" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P64" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D64,1)="K",VLOOKUP(D64,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D64,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15404,13 +15411,13 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="96" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B65" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C65" s="96" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D65" s="96" t="s">
         <v>557</v>
@@ -15453,7 +15460,7 @@
         <v>0.42922</v>
       </c>
       <c r="O65" s="102" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="P65" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D65,1)="K",VLOOKUP(D65,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D65,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15470,13 +15477,13 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="96" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B66" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C66" s="96" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D66" s="96" t="s">
         <v>536</v>
@@ -15519,7 +15526,7 @@
         <v>0.165366666666667</v>
       </c>
       <c r="O66" s="102" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P66" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D66,1)="K",VLOOKUP(D66,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D66,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15536,13 +15543,13 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="96" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B67" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C67" s="96" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D67" s="96" t="s">
         <v>540</v>
@@ -15585,7 +15592,7 @@
         <v>0.0826833333333333</v>
       </c>
       <c r="O67" s="102" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P67" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D67,1)="K",VLOOKUP(D67,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D67,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15602,13 +15609,13 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="96" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B68" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C68" s="96" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D68" s="96" t="s">
         <v>544</v>
@@ -15651,7 +15658,7 @@
         <v>0.395032</v>
       </c>
       <c r="O68" s="102" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P68" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D68,1)="K",VLOOKUP(D68,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D68,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15668,13 +15675,13 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="96" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B69" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C69" s="96" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="D69" s="96" t="s">
         <v>388</v>
@@ -15686,7 +15693,7 @@
         <v>1</v>
       </c>
       <c r="G69" s="96" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H69" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -15717,7 +15724,7 @@
         <v/>
       </c>
       <c r="O69" s="102" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="P69" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D69,1)="K",VLOOKUP(D69,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D69,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15734,13 +15741,13 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="96" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B70" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C70" s="96" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="D70" s="96" t="s">
         <v>614</v>
@@ -15783,7 +15790,7 @@
         <v/>
       </c>
       <c r="O70" s="102" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P70" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D70,1)="K",VLOOKUP(D70,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D70,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15800,13 +15807,13 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="96" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B71" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C71" s="96" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="D71" s="96" t="s">
         <v>619</v>
@@ -15849,7 +15856,7 @@
         <v/>
       </c>
       <c r="O71" s="102" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P71" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D71,1)="K",VLOOKUP(D71,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D71,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15866,13 +15873,13 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="96" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B72" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C72" s="96" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="D72" s="96" t="s">
         <v>435</v>
@@ -15915,7 +15922,7 @@
         <v/>
       </c>
       <c r="O72" s="102" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="P72" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D72,1)="K",VLOOKUP(D72,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D72,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15932,7 +15939,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="85" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B73" s="85" t="s">
         <v>901</v>
@@ -15950,7 +15957,7 @@
         <v>1</v>
       </c>
       <c r="G73" s="85" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H73" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -15981,7 +15988,7 @@
         <v>3437.5</v>
       </c>
       <c r="O73" s="94" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="P73" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D73,1)="K",VLOOKUP(D73,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D73,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15998,7 +16005,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="85" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B74" s="85" t="s">
         <v>901</v>
@@ -16016,7 +16023,7 @@
         <v>1</v>
       </c>
       <c r="G74" s="85" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H74" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -16047,7 +16054,7 @@
         <v>82.5</v>
       </c>
       <c r="O74" s="94" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="P74" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D74,1)="K",VLOOKUP(D74,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D74,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16064,7 +16071,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="85" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B75" s="85" t="s">
         <v>901</v>
@@ -16082,7 +16089,7 @@
         <v>1</v>
       </c>
       <c r="G75" s="85" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H75" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -16113,7 +16120,7 @@
         <v>22</v>
       </c>
       <c r="O75" s="94" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="P75" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D75,1)="K",VLOOKUP(D75,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D75,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16130,7 +16137,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="85" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B76" s="85" t="s">
         <v>901</v>
@@ -16179,7 +16186,7 @@
         <v>0.05203572</v>
       </c>
       <c r="O76" s="94" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P76" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D76,1)="K",VLOOKUP(D76,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D76,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16196,13 +16203,13 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="85" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B77" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C77" s="85" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D77" s="85" t="s">
         <v>346</v>
@@ -16245,7 +16252,7 @@
         <v>0.62348</v>
       </c>
       <c r="O77" s="94" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P77" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D77,1)="K",VLOOKUP(D77,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D77,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16262,13 +16269,13 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="85" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B78" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C78" s="85" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D78" s="85" t="s">
         <v>360</v>
@@ -16311,7 +16318,7 @@
         <v>9.717246</v>
       </c>
       <c r="O78" s="94" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P78" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D78,1)="K",VLOOKUP(D78,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D78,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16328,13 +16335,13 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="85" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B79" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C79" s="85" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D79" s="85" t="s">
         <v>375</v>
@@ -16346,7 +16353,7 @@
         <v>1</v>
       </c>
       <c r="G79" s="85" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H79" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -16377,7 +16384,7 @@
         <v/>
       </c>
       <c r="O79" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P79" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D79,1)="K",VLOOKUP(D79,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D79,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16394,13 +16401,13 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="85" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B80" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C80" s="85" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="D80" s="85" t="s">
         <v>367</v>
@@ -16412,7 +16419,7 @@
         <v>1</v>
       </c>
       <c r="G80" s="85" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H80" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -16443,7 +16450,7 @@
         <v>1.87726</v>
       </c>
       <c r="O80" s="94" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="P80" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D80,1)="K",VLOOKUP(D80,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D80,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16460,13 +16467,13 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="85" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B81" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C81" s="85" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="D81" s="85" t="s">
         <v>579</v>
@@ -16509,7 +16516,7 @@
         <v>0.594</v>
       </c>
       <c r="O81" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P81" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D81,1)="K",VLOOKUP(D81,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D81,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16526,13 +16533,13 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="85" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B82" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C82" s="85" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D82" s="85" t="s">
         <v>557</v>
@@ -16575,7 +16582,7 @@
         <v>0.21461</v>
       </c>
       <c r="O82" s="94" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="P82" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D82,1)="K",VLOOKUP(D82,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D82,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16592,13 +16599,13 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="85" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B83" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C83" s="85" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D83" s="85" t="s">
         <v>536</v>
@@ -16641,7 +16648,7 @@
         <v>0.124025</v>
       </c>
       <c r="O83" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P83" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D83,1)="K",VLOOKUP(D83,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D83,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16658,13 +16665,13 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="85" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B84" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C84" s="85" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D84" s="85" t="s">
         <v>544</v>
@@ -16707,7 +16714,7 @@
         <v>0.395032</v>
       </c>
       <c r="O84" s="94" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="P84" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D84,1)="K",VLOOKUP(D84,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D84,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16724,13 +16731,13 @@
     </row>
     <row r="85" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="85" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B85" s="85" t="s">
         <v>896</v>
       </c>
       <c r="C85" s="85" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="D85" s="85"/>
       <c r="E85" s="85" t="s">
@@ -16751,18 +16758,18 @@
       <c r="M85" s="105"/>
       <c r="N85" s="106"/>
       <c r="O85" s="94" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="85" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B86" s="85" t="s">
         <v>896</v>
       </c>
       <c r="C86" s="85" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="D86" s="85"/>
       <c r="E86" s="85" t="s">
@@ -16783,18 +16790,18 @@
       <c r="M86" s="105"/>
       <c r="N86" s="106"/>
       <c r="O86" s="94" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="85" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B87" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C87" s="85" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="D87" s="85" t="s">
         <v>301</v>
@@ -16806,7 +16813,7 @@
         <v>1</v>
       </c>
       <c r="G87" s="85" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H87" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -16837,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="O87" s="94" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="P87" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D87,1)="K",VLOOKUP(D87,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D87,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16854,7 +16861,7 @@
     </row>
     <row r="88" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="85" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B88" s="85" t="s">
         <v>901</v>
@@ -16903,7 +16910,7 @@
         <v>0</v>
       </c>
       <c r="O88" s="94" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="P88" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D88,1)="K",VLOOKUP(D88,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D88,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16920,7 +16927,7 @@
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="85" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B89" s="85" t="s">
         <v>901</v>
@@ -16969,7 +16976,7 @@
         <v>0</v>
       </c>
       <c r="O89" s="94" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="P89" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D89,1)="K",VLOOKUP(D89,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D89,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16986,7 +16993,7 @@
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="85" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B90" s="85" t="s">
         <v>901</v>
@@ -17035,7 +17042,7 @@
         <v>0</v>
       </c>
       <c r="O90" s="94" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="P90" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D90,1)="K",VLOOKUP(D90,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D90,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -17052,7 +17059,7 @@
     </row>
     <row r="91" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="85" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B91" s="85" t="s">
         <v>901</v>
@@ -17101,7 +17108,7 @@
         <v>0</v>
       </c>
       <c r="O91" s="94" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="P91" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D91,1)="K",VLOOKUP(D91,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D91,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -17118,13 +17125,13 @@
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="85" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B92" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C92" s="85" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="D92" s="85" t="s">
         <v>579</v>
@@ -17167,7 +17174,7 @@
         <v>0</v>
       </c>
       <c r="O92" s="94" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="P92" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D92,1)="K",VLOOKUP(D92,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D92,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -17184,13 +17191,13 @@
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="85" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B93" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C93" s="85" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="D93" s="85" t="s">
         <v>375</v>
@@ -17233,7 +17240,7 @@
         <v/>
       </c>
       <c r="O93" s="94" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="P93" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D93,1)="K",VLOOKUP(D93,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D93,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -17250,7 +17257,7 @@
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="85" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B94" s="85" t="s">
         <v>901</v>
@@ -17299,7 +17306,7 @@
         <v>0</v>
       </c>
       <c r="O94" s="94" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="P94" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D94,1)="K",VLOOKUP(D94,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D94,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -17405,7 +17412,7 @@
         <v>884</v>
       </c>
       <c r="D1" s="76" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E1" s="76" t="s">
         <v>888</v>
@@ -17416,7 +17423,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="96" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B2" s="96"/>
       <c r="C2" s="96" t="s">
@@ -17437,7 +17444,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="96" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B3" s="96"/>
       <c r="C3" s="96" t="s">
@@ -17550,20 +17557,20 @@
       </c>
       <c r="D8" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A8,Pre_GEM_Consumables!$G$2:$G$110,C8,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A8,Post_GEM_Consumables!$G$2:$G$97,C8,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
-        <v>7.128</v>
+        <v>17.82</v>
       </c>
       <c r="E8" s="108" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(C8,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(D8,0),ROUND(D8,2))</f>
-        <v>7.13</v>
+        <v>17.82</v>
       </c>
       <c r="F8" s="109" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$N$2:$N$110,Pre_GEM_Consumables!$C$2:$C$110,A8,Pre_GEM_Consumables!$G$2:$G$110,C8)+SUMIFS(Post_GEM_Consumables!$N$2:$N$97,Post_GEM_Consumables!$C$2:$C$97,A8,Post_GEM_Consumables!$G$2:$G$97,C8)</f>
-        <v>2.28096</v>
+        <v>5.7024</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="96" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B9" s="96"/>
       <c r="C9" s="96" t="s">
@@ -17626,7 +17633,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="96" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B12" s="96"/>
       <c r="C12" s="96" t="s">
@@ -17647,7 +17654,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="96" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B13" s="96"/>
       <c r="C13" s="96" t="s">
@@ -17668,7 +17675,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="96" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B14" s="96"/>
       <c r="C14" s="96" t="s">
@@ -17710,7 +17717,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="96" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B16" s="96"/>
       <c r="C16" s="96" t="s">
@@ -17731,7 +17738,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="96" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B17" s="96"/>
       <c r="C17" s="96" t="s">
@@ -17752,7 +17759,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="96" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B18" s="96"/>
       <c r="C18" s="96" t="s">
@@ -17794,7 +17801,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="96" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B20" s="96"/>
       <c r="C20" s="96" t="s">
@@ -17815,11 +17822,11 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="96" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B21" s="96"/>
       <c r="C21" s="96" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="D21" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A21,Pre_GEM_Consumables!$G$2:$G$110,C21,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A21,Post_GEM_Consumables!$G$2:$G$97,C21,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -17857,7 +17864,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="96" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B23" s="96"/>
       <c r="C23" s="96" t="s">
@@ -17878,7 +17885,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="96" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B24" s="96"/>
       <c r="C24" s="96" t="s">
@@ -17920,7 +17927,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="96" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B26" s="96"/>
       <c r="C26" s="96" t="s">
@@ -17983,7 +17990,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="96" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B29" s="96"/>
       <c r="C29" s="96" t="s">
@@ -18067,7 +18074,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="96" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B33" s="96"/>
       <c r="C33" s="96" t="s">
@@ -18088,7 +18095,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="96" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B34" s="96"/>
       <c r="C34" s="96" t="s">
@@ -18130,11 +18137,11 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="96" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B36" s="96"/>
       <c r="C36" s="96" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="D36" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A36,Pre_GEM_Consumables!$G$2:$G$110,C36,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A36,Post_GEM_Consumables!$G$2:$G$97,C36,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18151,7 +18158,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="96" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B37" s="96"/>
       <c r="C37" s="96" t="s">
@@ -18172,7 +18179,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="96" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B38" s="96"/>
       <c r="C38" s="96" t="s">
@@ -18193,7 +18200,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="96" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B39" s="96"/>
       <c r="C39" s="96" t="s">
@@ -18214,7 +18221,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="96" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B40" s="96"/>
       <c r="C40" s="96" t="s">
@@ -18235,7 +18242,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="96" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B41" s="96"/>
       <c r="C41" s="96" t="s">
@@ -18277,7 +18284,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="96" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B43" s="96"/>
       <c r="C43" s="96" t="s">
@@ -18298,7 +18305,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="96" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B44" s="96"/>
       <c r="C44" s="96" t="s">
@@ -18319,7 +18326,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="96" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B45" s="96"/>
       <c r="C45" s="96" t="s">
@@ -18340,11 +18347,11 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="96" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B46" s="96"/>
       <c r="C46" s="96" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D46" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A46,Pre_GEM_Consumables!$G$2:$G$110,C46,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A46,Post_GEM_Consumables!$G$2:$G$97,C46,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18365,7 +18372,7 @@
       </c>
       <c r="B47" s="96"/>
       <c r="C47" s="96" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D47" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A47,Pre_GEM_Consumables!$G$2:$G$110,C47,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A47,Post_GEM_Consumables!$G$2:$G$97,C47,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18386,7 +18393,7 @@
       </c>
       <c r="B48" s="96"/>
       <c r="C48" s="96" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D48" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A48,Pre_GEM_Consumables!$G$2:$G$110,C48,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A48,Post_GEM_Consumables!$G$2:$G$97,C48,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18407,7 +18414,7 @@
       </c>
       <c r="B49" s="96"/>
       <c r="C49" s="96" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D49" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A49,Pre_GEM_Consumables!$G$2:$G$110,C49,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A49,Post_GEM_Consumables!$G$2:$G$97,C49,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18428,7 +18435,7 @@
       </c>
       <c r="B50" s="96"/>
       <c r="C50" s="96" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D50" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A50,Pre_GEM_Consumables!$G$2:$G$110,C50,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A50,Post_GEM_Consumables!$G$2:$G$97,C50,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18449,7 +18456,7 @@
       </c>
       <c r="B51" s="96"/>
       <c r="C51" s="96" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D51" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A51,Pre_GEM_Consumables!$G$2:$G$110,C51,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A51,Post_GEM_Consumables!$G$2:$G$97,C51,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18470,7 +18477,7 @@
       </c>
       <c r="B52" s="96"/>
       <c r="C52" s="96" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D52" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A52,Pre_GEM_Consumables!$G$2:$G$110,C52,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A52,Post_GEM_Consumables!$G$2:$G$97,C52,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18491,7 +18498,7 @@
       </c>
       <c r="B53" s="96"/>
       <c r="C53" s="96" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D53" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A53,Pre_GEM_Consumables!$G$2:$G$110,C53,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A53,Post_GEM_Consumables!$G$2:$G$97,C53,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18512,7 +18519,7 @@
       </c>
       <c r="B54" s="96"/>
       <c r="C54" s="96" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D54" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A54,Pre_GEM_Consumables!$G$2:$G$110,C54,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A54,Post_GEM_Consumables!$G$2:$G$97,C54,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18533,7 +18540,7 @@
       </c>
       <c r="B55" s="96"/>
       <c r="C55" s="96" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D55" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A55,Pre_GEM_Consumables!$G$2:$G$110,C55,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A55,Post_GEM_Consumables!$G$2:$G$97,C55,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18554,7 +18561,7 @@
       </c>
       <c r="B56" s="96"/>
       <c r="C56" s="96" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D56" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A56,Pre_GEM_Consumables!$G$2:$G$110,C56,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A56,Post_GEM_Consumables!$G$2:$G$97,C56,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18575,7 +18582,7 @@
       </c>
       <c r="B57" s="96"/>
       <c r="C57" s="96" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D57" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A57,Pre_GEM_Consumables!$G$2:$G$110,C57,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A57,Post_GEM_Consumables!$G$2:$G$97,C57,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18613,7 +18620,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="96" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B59" s="96"/>
       <c r="C59" s="96" t="s">
@@ -18634,7 +18641,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="96" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B60" s="96"/>
       <c r="C60" s="96" t="s">
@@ -18655,11 +18662,11 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="96" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B61" s="96"/>
       <c r="C61" s="96" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="D61" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A61,Pre_GEM_Consumables!$G$2:$G$110,C61,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A61,Post_GEM_Consumables!$G$2:$G$97,C61,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18676,11 +18683,11 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="96" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B62" s="96"/>
       <c r="C62" s="96" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="D62" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A62,Pre_GEM_Consumables!$G$2:$G$110,C62,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A62,Post_GEM_Consumables!$G$2:$G$97,C62,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18697,7 +18704,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="96" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B63" s="96"/>
       <c r="C63" s="96" t="s">
@@ -18718,7 +18725,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="96" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B64" s="96"/>
       <c r="C64" s="96" t="s">
@@ -18739,7 +18746,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="96" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B65" s="96"/>
       <c r="C65" s="96" t="s">
@@ -18760,7 +18767,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="96" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B66" s="96"/>
       <c r="C66" s="96" t="s">
@@ -18781,7 +18788,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="96" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B67" s="96"/>
       <c r="C67" s="96" t="s">
@@ -18802,7 +18809,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="96" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B68" s="96"/>
       <c r="C68" s="96" t="s">
@@ -18823,7 +18830,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="96" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B69" s="96"/>
       <c r="C69" s="96" t="s">
@@ -18844,11 +18851,11 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="96" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B70" s="96"/>
       <c r="C70" s="96" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="D70" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A70,Pre_GEM_Consumables!$G$2:$G$110,C70,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A70,Post_GEM_Consumables!$G$2:$G$97,C70,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18865,7 +18872,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="96" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B71" s="96"/>
       <c r="C71" s="96" t="s">
@@ -18886,7 +18893,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="96" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B72" s="96"/>
       <c r="C72" s="96" t="s">
@@ -18907,7 +18914,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="96" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B73" s="96"/>
       <c r="C73" s="96" t="s">
@@ -18928,11 +18935,11 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="110" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="F75" s="111" t="n">
         <f aca="false">SUM(F2:F73)</f>
-        <v>32480.5653679393</v>
+        <v>32483.9868079393</v>
       </c>
     </row>
   </sheetData>
@@ -18964,12 +18971,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18977,15 +18984,15 @@
         <v>897</v>
       </c>
       <c r="D4" s="113" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="114" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B5" s="114" t="s">
         <v>1041</v>
-      </c>
-      <c r="B5" s="114" t="s">
-        <v>1042</v>
       </c>
       <c r="C5" s="114" t="s">
         <v>884</v>
@@ -18993,7 +19000,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B6" s="115" t="n">
         <v>1</v>
@@ -19004,7 +19011,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B7" s="115" t="n">
         <v>0.01</v>
@@ -19018,15 +19025,15 @@
         <v>900</v>
       </c>
       <c r="D9" s="113" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="114" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B10" s="114" t="s">
         <v>1041</v>
-      </c>
-      <c r="B10" s="114" t="s">
-        <v>1042</v>
       </c>
       <c r="C10" s="114" t="s">
         <v>884</v>
@@ -19034,7 +19041,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B11" s="115" t="n">
         <v>1</v>
@@ -19045,7 +19052,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B12" s="115" t="n">
         <v>0.0025</v>
@@ -19056,18 +19063,18 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="112" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="114" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B15" s="114" t="s">
         <v>1041</v>
-      </c>
-      <c r="B15" s="114" t="s">
-        <v>1042</v>
       </c>
       <c r="C15" s="114" t="s">
         <v>884</v>
@@ -19086,7 +19093,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B17" s="115" t="n">
         <v>1</v>
@@ -19097,18 +19104,18 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="112" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D19" s="113" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="114" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B20" s="114" t="s">
         <v>1041</v>
-      </c>
-      <c r="B20" s="114" t="s">
-        <v>1042</v>
       </c>
       <c r="C20" s="114" t="s">
         <v>884</v>
@@ -19127,7 +19134,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B22" s="115" t="n">
         <v>0.5</v>
@@ -19138,18 +19145,18 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="112" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D24" s="113" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="114" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B25" s="114" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C25" s="114" t="s">
         <v>884</v>
@@ -19190,7 +19197,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B29" s="115" t="n">
         <v>0.01</v>
@@ -19212,7 +19219,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B31" s="115" t="n">
         <v>0.01</v>
@@ -19223,7 +19230,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B32" s="115" t="n">
         <v>0.1</v>
@@ -19234,7 +19241,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B33" s="115" t="n">
         <v>0.863</v>
@@ -19245,18 +19252,18 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="112" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D35" s="113" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="114" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B36" s="114" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C36" s="114" t="s">
         <v>884</v>
@@ -19297,7 +19304,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B40" s="115" t="n">
         <v>0.1</v>
@@ -19308,7 +19315,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B41" s="115" t="n">
         <v>0.885</v>
@@ -19319,18 +19326,18 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="112" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D43" s="113" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="114" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B44" s="114" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C44" s="114" t="s">
         <v>884</v>
@@ -19338,7 +19345,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B45" s="115" t="n">
         <v>0.05</v>
@@ -19349,7 +19356,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B46" s="115" t="n">
         <v>0.95</v>
@@ -19360,18 +19367,18 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="112" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="D48" s="113" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="114" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B49" s="114" t="s">
         <v>1041</v>
-      </c>
-      <c r="B49" s="114" t="s">
-        <v>1042</v>
       </c>
       <c r="C49" s="114" t="s">
         <v>884</v>
@@ -19379,7 +19386,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B50" s="115" t="n">
         <v>1</v>
@@ -19390,7 +19397,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B51" s="115" t="n">
         <v>0.999</v>
@@ -19425,12 +19432,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="117" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B2" s="117"/>
       <c r="C2" s="117"/>
@@ -19441,10 +19448,10 @@
         <v>884</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>1054</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19455,7 +19462,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19466,18 +19473,18 @@
         <v>1000</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>1000000</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19488,7 +19495,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19499,18 +19506,18 @@
         <v>1000</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>0.001</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19521,7 +19528,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19532,7 +19539,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19543,7 +19550,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19554,7 +19561,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19565,7 +19572,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19576,7 +19583,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19587,40 +19594,40 @@
         <v>1</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19631,18 +19638,18 @@
         <v>1</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19653,51 +19660,51 @@
         <v>1</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19747,12 +19754,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="118" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19792,152 +19799,152 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
   </sheetData>
@@ -19973,12 +19980,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="118" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20018,152 +20025,152 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
   </sheetData>

--- a/data/SingleCell_Pipeline_MasterSchema.xlsx
+++ b/data/SingleCell_Pipeline_MasterSchema.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2893" uniqueCount="1129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2893" uniqueCount="1130">
   <si>
     <t xml:space="preserve">Experiment inputs</t>
   </si>
@@ -2755,390 +2755,396 @@
     <t xml:space="preserve">[no catalog price]</t>
   </si>
   <si>
+    <t xml:space="preserve">Nexcelom counting plate (24 samples/plate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thawsome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPMI (mL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPMI base for both media: thaw (J2) + low (J3). 1 mL RPMI per mL media.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dnase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNase from RPMI-DNase media: thaw 0.1 mg/mL + low 0.025 mg/mL (10 mg/mL stock at recipe dilution).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50mL conical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLCELLS control aliquot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aliquot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADDED (was missing): one control per pool. [no catalog price]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">III. Unsort CITE-seq stain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staining buffer (PBS+2% BSA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2mL eppendorf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5mL FACS tube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TotalseqC HTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fc Block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSA now tracked as grams of powder (2% w/v staining buffer = 0.02 g/mL). Enter powder $/g in Additional_Supply_Catalog R026. 0.28 g = 2% x 14 mL PBS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1X PBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TotalseqC Antibody Cocktail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSA now tracked as grams of powder (2% w/v staining buffer = 0.02 g/mL). Enter powder $/g in Additional_Supply_Catalog R026. 0.18 g = 2% x 9 mL PBS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IV. ASAP-seq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASAP lysis buffer (OMNI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASAP wash buffer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1X nuclei buffer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TotalseqA HTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSA (powder): ASAP HTO staining = CITE staining (0.28 g = 2% x 14 mL). Same wash procedure as unsort.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASAP HTO staining PBS = CITE staining (14 mL/pool). Same 3x pre + 3x post + resuspend washes as unsort. [ADAPTED to SOP: 19 mL/pool/modality (was 14).]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16% Formaldehyde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1M Tris-HCl (pH 7.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10% NP40/IPEGAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TotalseqA Antibody Cocktail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSA (powder): ASAP lyo-panel staining = CITE super-pool staining (0.18 g = 2% x 9 mL).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCR strip  tubes (strip)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V. Sort stain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FACS buffer (PBS+50% FBS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L/D Zombie Red (diluted stain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORRECTED 200-&gt;61.5: source adds 61.5 uL Ab cocktail + 5 uL HTO to 200 uL total tube vol; only 61.5 uL is antibody. MADI/AJ sort protocol.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORRECTED 20-&gt;10: source (AJ sort protocol) adds 10 uL Fc block per sort tube.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORRECTED 65-&gt;6: source uses 2x 2 mL 1X PBS washes/pool (~4 mL) + margin; 65 was implausible. Verify intended wash volume.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADDED (was missing): 250 uL diluted viability stain per sort pool. [no catalog price]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L/D Zombie Red stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADDED: 0.25 uL stock per pool (1:1000). [no catalog price]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADDED (was missing): single-stain comp for the sorter. [no catalog price]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unstained control (leukopak)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADDED (was missing). [no catalog price]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sort collection tube (population)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADDED (was missing): HSC/pDC/cDC/Treg. [no catalog price]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FACS tube filter cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADDED (was missing): filter before sort. [no catalog price]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VI. Bulk RNA (Trizol)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5mL eppendorf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRIzol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VII. Flex v2 (fixation → GEM load)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixation Buffer B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-sample recipe (CG000782): NF water 435 + Conc. Fix &amp; Perm Buffer B (PN-2001301) 55 + 37% formaldehyde 60 uL = 550 uL/sample. Components in Sample Prep v2 Kit; formaldehyde third-party.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quenching Buffer B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-sample recipe (CG000782): NF water 938 + Conc. Quench Buffer B (PN-2001300) 134 uL = ~1072 uL/sample (+0.5 mL/sample if storing).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe Hyb Mix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-sample (CG000834 Step 1): Hyb Buffer B 38.5 + Enhancer 5.5 + Additive A 2.75 + WTA Probes v2 8.25 = 55 uL/sample. Components in Core Reagents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-Hyb Wash Buffer B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-sample tube (CG000834 Step 3): NF water 445 + Enhancer 25 + Conc. Post-Hyb Buffer B 25 uL = 495 uL. Used at post-hyb pooled wash.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEM Master Mix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per GEM reaction (CG000834 Step 4.1): GEM Reagent Mix 19.9 + Reducing Agent B 1.6 + GEM Enzyme Mix B 11.8 = 33.3 uL. Components in GEM &amp; Library Kit / Core Reagents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT (PN-1000781). Fix/Perm B, Quench B, Enhancer, Additive C. 48 samples/kit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEM-X Flex v2 Core Reagents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT (PN-1000927, 16 samp). Hyb Buffer B, Additive A, WTA Probes v2, Barcoding Oligo plates, Conc. Post-Hyb Buffer B, GEM/pre-amp/library reagents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">channels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT (PN-1000791). GEM-X FX Chip (PN-2001257) + Partitioning Oil B. rxn/kit inferred 16 - verify.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT (PN-1000918, 4 rxn) - GEM Reagent Mix, Enzyme Mix B, Amp Mix C, Pre-Amp Primers B. Price unverified -&gt; uncosted; may overlap Core Reagents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formaldehyde 37%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixation Buffer B (CG000782). 37% BP531-25.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuclease-free Water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buffers (fixation/quench/hyb/wash). AM9937 recommended.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glycerol (for 50% soln)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50% glycerol for -80C storage / unused chip wells.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hybridization / handling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyb / GEM / PCR (strip shared across steps). 1 PCR tube per reaction; 8 tubes per strip.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 uL pipette tips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate across fixation-&gt;load steps.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TotalseqC HTO (sort)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADDED: source adds 5 uL TotalSeq-C HTO per sort pool (distinct hashtag/pool).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADDED: 2 mL staining buffer wash/pool (source line 742) = 0.04 g BSA (2%). PBS for it is in the 6 mL sort PBS row.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADDED: lyo-panel staining PBS for ASAP super-pool = CITE super-pool (9 mL). Fixation-wash PBS stays on the 2.45 mL row.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-GEM: 5'-GEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUPPLY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethanol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPRISelect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCR strip  tubes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(manual) [no catalog price] 1 PCR tube per reaction; 8 tubes per strip.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1000uL pipette tips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(manual) [no catalog price]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200uL pipette tips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20uL pipette tips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eppendorf Tubes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUPPLY [no catalog price]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TapeStation HS D5000 kit (cDNA/amplicon QC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-GEM: ATAC-GEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-GEM: 5'-GEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tapestation HS D1000 kit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qubit Assay Reagent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qubit Assay Tubes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAPA Library Quant (qPCR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-GEM: 5'-VDJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-GEM: 5'-ADT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-GEM: ATAC-ADT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2x KAPA HiFi mix (ASAP tag PCR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3'-ASAP-P5 primer (10uM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPxx / D7xx index primer (10uM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-GEM: ATAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-GEM: Flex v2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-Amplification Mix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per GEM reaction (CG000834 Step 5.2): Amp Mix C 25 + Pre-Amp Primers B 10 = 35 uL. Components in GEM &amp; Library Kit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample Index PCR Mix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per library (CG000834 Step 6.1, &lt;=320k cells): Amp Mix C 50 + NF water 10 = 60 uL. + 20 uL Dual Index TS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dual Index Plate TS, Set A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT (PN-1000251 / plate PN-3000511). One unique index well per library. 96 rxn/kit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-amp cleanup + post-SI-PCR size selection (SI-PCR 1.0X = 100 uL/library).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elution (pre-amp cleanup + SI-PCR 41 uL).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80% ethanol washes (pre-amp + SI-PCR, 2x200 uL each).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-library QC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TapeStation HS D1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-library QC trace.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-amp / SI-PCR / library. 1 PCR tube per reaction; 8 tubes per strip.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 uL tips</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nexcelom counting plate (lane)</t>
   </si>
   <si>
     <t xml:space="preserve">lane</t>
   </si>
   <si>
-    <t xml:space="preserve">Thawsome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPMI (mL)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPMI base for both media: thaw (J2) + low (J3). 1 mL RPMI per mL media.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dnase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNase from RPMI-DNase media: thaw 0.1 mg/mL + low 0.025 mg/mL (10 mg/mL stock at recipe dilution).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50mL conical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLCELLS control aliquot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aliquot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADDED (was missing): one control per pool. [no catalog price]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">III. Unsort CITE-seq stain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staining buffer (PBS+2% BSA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2mL eppendorf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5mL FACS tube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TotalseqC HTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fc Block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSA now tracked as grams of powder (2% w/v staining buffer = 0.02 g/mL). Enter powder $/g in Additional_Supply_Catalog R026. 0.28 g = 2% x 14 mL PBS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1X PBS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TotalseqC Antibody Cocktail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSA now tracked as grams of powder (2% w/v staining buffer = 0.02 g/mL). Enter powder $/g in Additional_Supply_Catalog R026. 0.18 g = 2% x 9 mL PBS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IV. ASAP-seq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASAP lysis buffer (OMNI)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASAP wash buffer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1X nuclei buffer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TotalseqA HTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSA (powder): ASAP HTO staining = CITE staining (0.28 g = 2% x 14 mL). Same wash procedure as unsort.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASAP HTO staining PBS = CITE staining (14 mL/pool). Same 3x pre + 3x post + resuspend washes as unsort. [ADAPTED to SOP: 19 mL/pool/modality (was 14).]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16% Formaldehyde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1M Tris-HCl (pH 7.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10% NP40/IPEGAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TotalseqA Antibody Cocktail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSA (powder): ASAP lyo-panel staining = CITE super-pool staining (0.18 g = 2% x 9 mL).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCR strip  tubes (strip)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V. Sort stain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FACS buffer (PBS+50% FBS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L/D Zombie Red (diluted stain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORRECTED 200-&gt;61.5: source adds 61.5 uL Ab cocktail + 5 uL HTO to 200 uL total tube vol; only 61.5 uL is antibody. MADI/AJ sort protocol.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORRECTED 20-&gt;10: source (AJ sort protocol) adds 10 uL Fc block per sort tube.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORRECTED 65-&gt;6: source uses 2x 2 mL 1X PBS washes/pool (~4 mL) + margin; 65 was implausible. Verify intended wash volume.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADDED (was missing): 250 uL diluted viability stain per sort pool. [no catalog price]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L/D Zombie Red stock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADDED: 0.25 uL stock per pool (1:1000). [no catalog price]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADDED (was missing): single-stain comp for the sorter. [no catalog price]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unstained control (leukopak)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADDED (was missing). [no catalog price]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sort collection tube (population)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADDED (was missing): HSC/pDC/cDC/Treg. [no catalog price]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FACS tube filter cap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADDED (was missing): filter before sort. [no catalog price]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VI. Bulk RNA (Trizol)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5mL eppendorf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRIzol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VII. Flex v2 (fixation → GEM load)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixation Buffer B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per-sample recipe (CG000782): NF water 435 + Conc. Fix &amp; Perm Buffer B (PN-2001301) 55 + 37% formaldehyde 60 uL = 550 uL/sample. Components in Sample Prep v2 Kit; formaldehyde third-party.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quenching Buffer B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per-sample recipe (CG000782): NF water 938 + Conc. Quench Buffer B (PN-2001300) 134 uL = ~1072 uL/sample (+0.5 mL/sample if storing).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Probe Hyb Mix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per-sample (CG000834 Step 1): Hyb Buffer B 38.5 + Enhancer 5.5 + Additive A 2.75 + WTA Probes v2 8.25 = 55 uL/sample. Components in Core Reagents.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post-Hyb Wash Buffer B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per-sample tube (CG000834 Step 3): NF water 445 + Enhancer 25 + Conc. Post-Hyb Buffer B 25 uL = 495 uL. Used at post-hyb pooled wash.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GEM Master Mix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per GEM reaction (CG000834 Step 4.1): GEM Reagent Mix 19.9 + Reducing Agent B 1.6 + GEM Enzyme Mix B 11.8 = 33.3 uL. Components in GEM &amp; Library Kit / Core Reagents.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT (PN-1000781). Fix/Perm B, Quench B, Enhancer, Additive C. 48 samples/kit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GEM-X Flex v2 Core Reagents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT (PN-1000927, 16 samp). Hyb Buffer B, Additive A, WTA Probes v2, Barcoding Oligo plates, Conc. Post-Hyb Buffer B, GEM/pre-amp/library reagents.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">channels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT (PN-1000791). GEM-X FX Chip (PN-2001257) + Partitioning Oil B. rxn/kit inferred 16 - verify.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT (PN-1000918, 4 rxn) - GEM Reagent Mix, Enzyme Mix B, Amp Mix C, Pre-Amp Primers B. Price unverified -&gt; uncosted; may overlap Core Reagents.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formaldehyde 37%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixation Buffer B (CG000782). 37% BP531-25.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuclease-free Water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buffers (fixation/quench/hyb/wash). AM9937 recommended.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glycerol (for 50% soln)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50% glycerol for -80C storage / unused chip wells.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hybridization / handling.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyb / GEM / PCR (strip shared across steps). 1 PCR tube per reaction; 8 tubes per strip.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200 uL pipette tips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate across fixation-&gt;load steps.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TotalseqC HTO (sort)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADDED: source adds 5 uL TotalSeq-C HTO per sort pool (distinct hashtag/pool).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADDED: 2 mL staining buffer wash/pool (source line 742) = 0.04 g BSA (2%). PBS for it is in the 6 mL sort PBS row.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADDED: lyo-panel staining PBS for ASAP super-pool = CITE super-pool (9 mL). Fixation-wash PBS stays on the 2.45 mL row.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post-GEM: 5'-GEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPPLY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethanol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPRISelect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCR strip  tubes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(manual) [no catalog price] 1 PCR tube per reaction; 8 tubes per strip.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1000uL pipette tips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(manual) [no catalog price]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200uL pipette tips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20uL pipette tips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eppendorf Tubes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPPLY [no catalog price]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TapeStation HS D5000 kit (cDNA/amplicon QC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post-GEM: ATAC-GEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post-GEM: 5'-GEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tapestation HS D1000 kit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">library</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qubit Assay Reagent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qubit Assay Tubes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAPA Library Quant (qPCR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post-GEM: 5'-VDJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post-GEM: 5'-ADT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post-GEM: ATAC-ADT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2x KAPA HiFi mix (ASAP tag PCR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3'-ASAP-P5 primer (10uM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPxx / D7xx index primer (10uM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post-GEM: ATAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post-GEM: Flex v2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre-Amplification Mix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per GEM reaction (CG000834 Step 5.2): Amp Mix C 25 + Pre-Amp Primers B 10 = 35 uL. Components in GEM &amp; Library Kit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sample Index PCR Mix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per library (CG000834 Step 6.1, &lt;=320k cells): Amp Mix C 50 + NF water 10 = 60 uL. + 20 uL Dual Index TS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dual Index Plate TS, Set A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT (PN-1000251 / plate PN-3000511). One unique index well per library. 96 rxn/kit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre-amp cleanup + post-SI-PCR size selection (SI-PCR 1.0X = 100 uL/library).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elution (pre-amp cleanup + SI-PCR 41 uL).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80% ethanol washes (pre-amp + SI-PCR, 2x200 uL each).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post-library QC.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TapeStation HS D1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post-library QC trace.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre-amp / SI-PCR / library. 1 PCR tube per reaction; 8 tubes per strip.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200 uL tips</t>
-  </si>
-  <si>
     <t xml:space="preserve">BSA (10% or mass)</t>
   </si>
   <si>
@@ -3248,9 +3254,6 @@
   </si>
   <si>
     <t xml:space="preserve">OL002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OL003</t>
   </si>
   <si>
     <t xml:space="preserve">OL004</t>
@@ -4862,7 +4865,7 @@
       </c>
       <c r="H5" s="7" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$N$2:$N$102,Pre_GEM_Consumables!$E$2:$E$102,G5)+SUMIFS(Post_GEM_Consumables!$N$2:$N$97,Post_GEM_Consumables!$E$2:$E$97,G5)</f>
-        <v>2205.131808</v>
+        <v>751.552438593</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5672,10 +5675,10 @@
         <v>9</v>
       </c>
       <c r="F5" s="86" t="n">
-        <v>1</v>
+        <v>0.041667</v>
       </c>
       <c r="G5" s="85" t="s">
-        <v>905</v>
+        <v>566</v>
       </c>
       <c r="H5" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -5687,11 +5690,11 @@
       </c>
       <c r="J5" s="89" t="n">
         <f aca="false">F5*I5*(1+H5)</f>
-        <v>59.4</v>
+        <v>2.4750198</v>
       </c>
       <c r="K5" s="90" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(G5,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J5,0),ROUND(J5,2))</f>
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="L5" s="91" t="n">
         <f aca="false">IFERROR(IF(OR(D5="",P5="",Q5="",Q5=0),"",IF(VLOOKUP(R5,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G5,Unit_Conversions!$A$5:$C$28,3,FALSE()),P5*VLOOKUP(G5,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q5*VLOOKUP(R5,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
@@ -5699,11 +5702,11 @@
       </c>
       <c r="M5" s="92" t="n">
         <f aca="false">IFERROR(F5*L5,"")</f>
-        <v>25.535</v>
+        <v>1.063966845</v>
       </c>
       <c r="N5" s="93" t="n">
         <f aca="false">IFERROR(J5*L5,"")</f>
-        <v>1516.779</v>
+        <v>63.199630593</v>
       </c>
       <c r="O5" s="94" t="s">
         <v>903</v>
@@ -5729,7 +5732,7 @@
         <v>901</v>
       </c>
       <c r="C6" s="85" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D6" s="85" t="s">
         <v>568</v>
@@ -5795,7 +5798,7 @@
         <v>901</v>
       </c>
       <c r="C7" s="85" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D7" s="85" t="s">
         <v>473</v>
@@ -5838,7 +5841,7 @@
         <v>11.902968</v>
       </c>
       <c r="O7" s="94" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="P7" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D7,1)="K",VLOOKUP(D7,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D7,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -5925,7 +5928,7 @@
         <v>901</v>
       </c>
       <c r="C9" s="85" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="D9" s="85" t="s">
         <v>483</v>
@@ -5968,7 +5971,7 @@
         <v>292.5714</v>
       </c>
       <c r="O9" s="94" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="P9" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D9,1)="K",VLOOKUP(D9,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D9,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -6057,7 +6060,7 @@
         <v>901</v>
       </c>
       <c r="C11" s="85" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D11" s="85" t="s">
         <v>555</v>
@@ -6123,7 +6126,7 @@
         <v>901</v>
       </c>
       <c r="C12" s="85" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D12" s="85" t="s">
         <v>555</v>
@@ -6189,7 +6192,7 @@
         <v>901</v>
       </c>
       <c r="C13" s="85" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D13" s="85"/>
       <c r="E13" s="85" t="s">
@@ -6199,7 +6202,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="85" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H13" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -6230,7 +6233,7 @@
         <v/>
       </c>
       <c r="O13" s="94" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="P13" s="1" t="str">
         <f aca="false">IFERROR(IF(LEFT(D13,1)="K",VLOOKUP(D13,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D13,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -6247,13 +6250,13 @@
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="77" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B14" s="77" t="s">
         <v>896</v>
       </c>
       <c r="C14" s="78" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D14" s="77"/>
       <c r="E14" s="77" t="s">
@@ -6279,13 +6282,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="96" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B15" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C15" s="96" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D15" s="96" t="s">
         <v>551</v>
@@ -6343,13 +6346,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="96" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B16" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C16" s="96" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D16" s="96" t="s">
         <v>555</v>
@@ -6409,7 +6412,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="96" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B17" s="96" t="s">
         <v>901</v>
@@ -6473,13 +6476,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="96" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B18" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C18" s="96" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D18" s="96" t="s">
         <v>584</v>
@@ -6539,13 +6542,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="96" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B19" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C19" s="96" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D19" s="96" t="s">
         <v>428</v>
@@ -6603,13 +6606,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="96" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B20" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C20" s="96" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D20" s="96" t="s">
         <v>431</v>
@@ -6667,7 +6670,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="96" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B21" s="96" t="s">
         <v>901</v>
@@ -6716,7 +6719,7 @@
         <v>10.413216</v>
       </c>
       <c r="O21" s="102" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="P21" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D21,1)="K",VLOOKUP(D21,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D21,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -6733,13 +6736,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="96" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B22" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C22" s="96" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D22" s="96" t="s">
         <v>339</v>
@@ -6797,13 +6800,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="96" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B23" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C23" s="96" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D23" s="96" t="s">
         <v>421</v>
@@ -6861,13 +6864,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="96" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B24" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C24" s="96" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D24" s="96" t="s">
         <v>339</v>
@@ -6925,7 +6928,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="96" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B25" s="96" t="s">
         <v>901</v>
@@ -6974,7 +6977,7 @@
         <v>0.822096</v>
       </c>
       <c r="O25" s="102" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="P25" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D25,1)="K",VLOOKUP(D25,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D25,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -6991,13 +6994,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="96" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B26" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C26" s="96" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D26" s="96" t="s">
         <v>551</v>
@@ -7055,13 +7058,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="96" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B27" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C27" s="96" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D27" s="96" t="s">
         <v>555</v>
@@ -7121,7 +7124,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="96" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B28" s="96" t="s">
         <v>901</v>
@@ -7185,13 +7188,13 @@
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="77" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B29" s="77" t="s">
         <v>896</v>
       </c>
       <c r="C29" s="78" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D29" s="77"/>
       <c r="E29" s="77" t="s">
@@ -7217,13 +7220,13 @@
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="77" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B30" s="77" t="s">
         <v>896</v>
       </c>
       <c r="C30" s="78" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D30" s="77"/>
       <c r="E30" s="77" t="s">
@@ -7249,13 +7252,13 @@
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="77" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B31" s="77" t="s">
         <v>896</v>
       </c>
       <c r="C31" s="78" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D31" s="77"/>
       <c r="E31" s="77" t="s">
@@ -7281,13 +7284,13 @@
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="77" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B32" s="77" t="s">
         <v>896</v>
       </c>
       <c r="C32" s="78" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D32" s="77"/>
       <c r="E32" s="77" t="s">
@@ -7313,13 +7316,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B33" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C33" s="85" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D33" s="85" t="s">
         <v>551</v>
@@ -7377,13 +7380,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B34" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C34" s="85" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D34" s="85" t="s">
         <v>555</v>
@@ -7443,7 +7446,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B35" s="85" t="s">
         <v>901</v>
@@ -7507,13 +7510,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B36" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C36" s="85" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D36" s="85" t="s">
         <v>584</v>
@@ -7573,13 +7576,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B37" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C37" s="85" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D37" s="85" t="s">
         <v>424</v>
@@ -7637,13 +7640,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B38" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C38" s="85" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D38" s="85" t="s">
         <v>431</v>
@@ -7701,7 +7704,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B39" s="85" t="s">
         <v>901</v>
@@ -7750,7 +7753,7 @@
         <v>10.413216</v>
       </c>
       <c r="O39" s="94" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="P39" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D39,1)="K",VLOOKUP(D39,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D39,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -7767,13 +7770,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B40" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C40" s="85" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D40" s="85" t="s">
         <v>339</v>
@@ -7816,7 +7819,7 @@
         <v>4.770216</v>
       </c>
       <c r="O40" s="94" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="P40" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D40,1)="K",VLOOKUP(D40,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D40,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -7833,13 +7836,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B41" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C41" s="85" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D41" s="85" t="s">
         <v>393</v>
@@ -7897,7 +7900,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B42" s="85" t="s">
         <v>901</v>
@@ -7961,13 +7964,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B43" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C43" s="85" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D43" s="85" t="s">
         <v>438</v>
@@ -8025,7 +8028,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B44" s="85" t="s">
         <v>901</v>
@@ -8089,7 +8092,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B45" s="85" t="s">
         <v>901</v>
@@ -8153,13 +8156,13 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B46" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C46" s="85" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D46" s="85" t="s">
         <v>455</v>
@@ -8217,7 +8220,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B47" s="85" t="s">
         <v>901</v>
@@ -8281,7 +8284,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B48" s="85" t="s">
         <v>901</v>
@@ -8345,7 +8348,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B49" s="85" t="s">
         <v>901</v>
@@ -8354,7 +8357,7 @@
         <v>411</v>
       </c>
       <c r="D49" s="85" t="s">
-        <v>410</v>
+        <v>934</v>
       </c>
       <c r="E49" s="85" t="s">
         <v>13</v>
@@ -8396,22 +8399,22 @@
       <c r="O49" s="94" t="s">
         <v>903</v>
       </c>
-      <c r="P49" s="1" t="n">
+      <c r="P49" s="1" t="str">
         <f aca="false">IFERROR(IF(LEFT(D49,1)="K",VLOOKUP(D49,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D49,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q49" s="1" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="1" t="str">
         <f aca="false">IFERROR(IF(LEFT(D49,1)="K",VLOOKUP(D49,Kit_Catalog!$A:$K,7,FALSE()),VLOOKUP(D49,Additional_Supply_Catalog!$A:$K,8,FALSE())),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R49" s="1" t="str">
         <f aca="false">IFERROR(IF(LEFT(D49,1)="K","rxn",VLOOKUP(D49,Additional_Supply_Catalog!$A:$K,9,FALSE())),"")</f>
-        <v>uL</v>
+        <v/>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B50" s="85" t="s">
         <v>901</v>
@@ -8475,13 +8478,13 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B51" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C51" s="85" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D51" s="85" t="s">
         <v>339</v>
@@ -8539,7 +8542,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B52" s="85" t="s">
         <v>901</v>
@@ -8605,7 +8608,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B53" s="85" t="s">
         <v>901</v>
@@ -8671,13 +8674,13 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B54" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C54" s="85" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D54" s="85" t="s">
         <v>551</v>
@@ -8735,13 +8738,13 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B55" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C55" s="85" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D55" s="85" t="s">
         <v>555</v>
@@ -8801,7 +8804,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B56" s="85" t="s">
         <v>901</v>
@@ -8865,7 +8868,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="85" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B57" s="85" t="s">
         <v>901</v>
@@ -8999,7 +9002,7 @@
         <v>901</v>
       </c>
       <c r="C60" s="78" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D60" s="77" t="s">
         <v>584</v>
@@ -9131,7 +9134,7 @@
         <v>901</v>
       </c>
       <c r="C62" s="96" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D62" s="96" t="s">
         <v>431</v>
@@ -9261,7 +9264,7 @@
         <v>901</v>
       </c>
       <c r="C64" s="96" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D64" s="96" t="s">
         <v>339</v>
@@ -11097,13 +11100,13 @@
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>901</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>339</v>
@@ -17486,28 +17489,28 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="96" t="s">
-        <v>904</v>
+        <v>1032</v>
       </c>
       <c r="B5" s="96"/>
       <c r="C5" s="96" t="s">
-        <v>905</v>
+        <v>1033</v>
       </c>
       <c r="D5" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A5,Pre_GEM_Consumables!$G$2:$G$110,C5,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A5,Post_GEM_Consumables!$G$2:$G$97,C5,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
-        <v>59.4</v>
+        <v>0</v>
       </c>
       <c r="E5" s="108" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(C5,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(D5,0),ROUND(D5,2))</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F5" s="109" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$N$2:$N$110,Pre_GEM_Consumables!$C$2:$C$110,A5,Pre_GEM_Consumables!$G$2:$G$110,C5)+SUMIFS(Post_GEM_Consumables!$N$2:$N$97,Post_GEM_Consumables!$C$2:$C$97,A5,Post_GEM_Consumables!$G$2:$G$97,C5)</f>
-        <v>1516.779</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="96" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B6" s="96"/>
       <c r="C6" s="96" t="s">
@@ -17528,7 +17531,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="96" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B7" s="96"/>
       <c r="C7" s="96" t="s">
@@ -17570,7 +17573,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="96" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B9" s="96"/>
       <c r="C9" s="96" t="s">
@@ -17654,7 +17657,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="96" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B13" s="96"/>
       <c r="C13" s="96" t="s">
@@ -17675,7 +17678,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="96" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B14" s="96"/>
       <c r="C14" s="96" t="s">
@@ -17717,7 +17720,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="96" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B16" s="96"/>
       <c r="C16" s="96" t="s">
@@ -17738,7 +17741,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="96" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B17" s="96"/>
       <c r="C17" s="96" t="s">
@@ -17759,7 +17762,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="96" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B18" s="96"/>
       <c r="C18" s="96" t="s">
@@ -17801,7 +17804,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="96" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B20" s="96"/>
       <c r="C20" s="96" t="s">
@@ -17822,11 +17825,11 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="96" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B21" s="96"/>
       <c r="C21" s="96" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="D21" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A21,Pre_GEM_Consumables!$G$2:$G$110,C21,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A21,Post_GEM_Consumables!$G$2:$G$97,C21,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -17864,7 +17867,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="96" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B23" s="96"/>
       <c r="C23" s="96" t="s">
@@ -17885,7 +17888,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="96" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B24" s="96"/>
       <c r="C24" s="96" t="s">
@@ -17927,7 +17930,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="96" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B26" s="96"/>
       <c r="C26" s="96" t="s">
@@ -17990,7 +17993,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="96" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B29" s="96"/>
       <c r="C29" s="96" t="s">
@@ -18095,7 +18098,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="96" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B34" s="96"/>
       <c r="C34" s="96" t="s">
@@ -18137,11 +18140,11 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="96" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B36" s="96"/>
       <c r="C36" s="96" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="D36" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A36,Pre_GEM_Consumables!$G$2:$G$110,C36,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A36,Post_GEM_Consumables!$G$2:$G$97,C36,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18158,7 +18161,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="96" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B37" s="96"/>
       <c r="C37" s="96" t="s">
@@ -18200,7 +18203,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="96" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="B39" s="96"/>
       <c r="C39" s="96" t="s">
@@ -18347,11 +18350,11 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="96" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B46" s="96"/>
       <c r="C46" s="96" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D46" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A46,Pre_GEM_Consumables!$G$2:$G$110,C46,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A46,Post_GEM_Consumables!$G$2:$G$97,C46,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18935,11 +18938,11 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="110" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="F75" s="111" t="n">
         <f aca="false">SUM(F2:F73)</f>
-        <v>32483.9868079393</v>
+        <v>30967.2078079393</v>
       </c>
     </row>
   </sheetData>
@@ -18971,12 +18974,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18984,15 +18987,15 @@
         <v>897</v>
       </c>
       <c r="D4" s="113" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="114" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="C5" s="114" t="s">
         <v>884</v>
@@ -19000,7 +19003,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="B6" s="115" t="n">
         <v>1</v>
@@ -19011,7 +19014,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="B7" s="115" t="n">
         <v>0.01</v>
@@ -19025,15 +19028,15 @@
         <v>900</v>
       </c>
       <c r="D9" s="113" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="114" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B10" s="114" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="C10" s="114" t="s">
         <v>884</v>
@@ -19041,7 +19044,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="B11" s="115" t="n">
         <v>1</v>
@@ -19052,7 +19055,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="B12" s="115" t="n">
         <v>0.0025</v>
@@ -19063,18 +19066,18 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="112" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="114" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B15" s="114" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="C15" s="114" t="s">
         <v>884</v>
@@ -19093,7 +19096,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B17" s="115" t="n">
         <v>1</v>
@@ -19107,15 +19110,15 @@
         <v>939</v>
       </c>
       <c r="D19" s="113" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="114" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B20" s="114" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="C20" s="114" t="s">
         <v>884</v>
@@ -19134,7 +19137,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B22" s="115" t="n">
         <v>0.5</v>
@@ -19145,18 +19148,18 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="112" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D24" s="113" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="114" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B25" s="114" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C25" s="114" t="s">
         <v>884</v>
@@ -19197,7 +19200,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B29" s="115" t="n">
         <v>0.01</v>
@@ -19219,7 +19222,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="B31" s="115" t="n">
         <v>0.01</v>
@@ -19230,7 +19233,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B32" s="115" t="n">
         <v>0.1</v>
@@ -19241,7 +19244,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B33" s="115" t="n">
         <v>0.863</v>
@@ -19252,18 +19255,18 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="112" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D35" s="113" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="114" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B36" s="114" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C36" s="114" t="s">
         <v>884</v>
@@ -19304,7 +19307,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B40" s="115" t="n">
         <v>0.1</v>
@@ -19315,7 +19318,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B41" s="115" t="n">
         <v>0.885</v>
@@ -19326,18 +19329,18 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="112" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D43" s="113" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="114" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B44" s="114" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C44" s="114" t="s">
         <v>884</v>
@@ -19345,7 +19348,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="B45" s="115" t="n">
         <v>0.05</v>
@@ -19356,7 +19359,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B46" s="115" t="n">
         <v>0.95</v>
@@ -19370,15 +19373,15 @@
         <v>940</v>
       </c>
       <c r="D48" s="113" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="114" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B49" s="114" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="C49" s="114" t="s">
         <v>884</v>
@@ -19397,7 +19400,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B51" s="115" t="n">
         <v>0.999</v>
@@ -19432,12 +19435,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="117" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B2" s="117"/>
       <c r="C2" s="117"/>
@@ -19448,10 +19451,10 @@
         <v>884</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19462,7 +19465,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19473,18 +19476,18 @@
         <v>1000</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>1000000</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19495,7 +19498,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19506,18 +19509,18 @@
         <v>1000</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>0.001</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19528,7 +19531,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19539,7 +19542,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19550,7 +19553,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19561,7 +19564,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19572,7 +19575,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19583,29 +19586,29 @@
         <v>1</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>905</v>
+        <v>1033</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19616,7 +19619,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19627,7 +19630,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19638,18 +19641,18 @@
         <v>1</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19660,51 +19663,51 @@
         <v>1</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19754,12 +19757,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="118" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19799,152 +19802,152 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1069</v>
+        <v>934</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
   </sheetData>
@@ -19980,12 +19983,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="118" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20025,152 +20028,152 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
   </sheetData>

--- a/data/SingleCell_Pipeline_MasterSchema.xlsx
+++ b/data/SingleCell_Pipeline_MasterSchema.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2893" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2907" uniqueCount="1133">
   <si>
     <t xml:space="preserve">Experiment inputs</t>
   </si>
@@ -2992,6 +2992,9 @@
     <t xml:space="preserve">200 uL pipette tips</t>
   </si>
   <si>
+    <t xml:space="preserve">rack</t>
+  </si>
+  <si>
     <t xml:space="preserve">Estimate across fixation-&gt;load steps.</t>
   </si>
   <si>
@@ -3005,6 +3008,12 @@
   </si>
   <si>
     <t xml:space="preserve">ADDED: lyo-panel staining PBS for ASAP super-pool = CITE super-pool (9 mL). Fixation-wash PBS stays on the 2.45 mL row.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20uL pipette tips (cell count)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1000uL pipette tips (thaw handling)</t>
   </si>
   <si>
     <t xml:space="preserve">Post-GEM: 5'-GEM</t>
@@ -4997,7 +5006,7 @@
       </c>
       <c r="H11" s="7" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$N$2:$N$102,Pre_GEM_Consumables!$E$2:$E$102,G11)+SUMIFS(Post_GEM_Consumables!$N$2:$N$97,Post_GEM_Consumables!$E$2:$E$97,G11)</f>
-        <v>13743.3683536417</v>
+        <v>13742.4392776</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5019,7 +5028,7 @@
       </c>
       <c r="H12" s="7" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$N$2:$N$102,Pre_GEM_Consumables!$E$2:$E$102,G12)+SUMIFS(Post_GEM_Consumables!$N$2:$N$97,Post_GEM_Consumables!$E$2:$E$97,G12)</f>
-        <v>838.899703253333</v>
+        <v>838.07286992</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5041,7 +5050,7 @@
       </c>
       <c r="H13" s="7" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$N$2:$N$102,Pre_GEM_Consumables!$E$2:$E$102,G13)+SUMIFS(Post_GEM_Consumables!$N$2:$N$97,Post_GEM_Consumables!$E$2:$E$97,G13)</f>
-        <v>1265.98062682667</v>
+        <v>1264.82306016</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5063,7 +5072,7 @@
       </c>
       <c r="H14" s="7" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$N$2:$N$102,Pre_GEM_Consumables!$E$2:$E$102,G14)+SUMIFS(Post_GEM_Consumables!$N$2:$N$97,Post_GEM_Consumables!$E$2:$E$97,G14)</f>
-        <v>499.342381706667</v>
+        <v>498.68091504</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5085,7 +5094,7 @@
       </c>
       <c r="H15" s="7" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$N$2:$N$102,Pre_GEM_Consumables!$E$2:$E$102,G15)+SUMIFS(Post_GEM_Consumables!$N$2:$N$97,Post_GEM_Consumables!$E$2:$E$97,G15)</f>
-        <v>3555.59768872</v>
+        <v>3555.47366372</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5107,7 +5116,7 @@
       </c>
       <c r="H16" s="7" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$N$2:$N$102,Pre_GEM_Consumables!$E$2:$E$102,G16)+SUMIFS(Post_GEM_Consumables!$N$2:$N$97,Post_GEM_Consumables!$E$2:$E$97,G16)</f>
-        <v>25.04997924</v>
+        <v>24.80192924</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5452,7 +5461,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R105"/>
+  <dimension ref="A1:R107"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
@@ -10679,10 +10688,10 @@
         <v>36</v>
       </c>
       <c r="F88" s="88" t="n">
-        <v>6</v>
+        <v>0.37917</v>
       </c>
       <c r="G88" s="85" t="s">
-        <v>534</v>
+        <v>983</v>
       </c>
       <c r="H88" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -10700,20 +10709,20 @@
         <f aca="false">IF(ISNUMBER(MATCH(G88,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J88,0),ROUND(J88,2))</f>
         <v>0</v>
       </c>
-      <c r="L88" s="105" t="n">
+      <c r="L88" s="105" t="str">
         <f aca="false">IFERROR(IF(OR(D88="",P88="",Q88="",Q88=0),"",IF(VLOOKUP(R88,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G88,Unit_Conversions!$A$5:$C$28,3,FALSE()),P88*VLOOKUP(G88,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q88*VLOOKUP(R88,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
-        <v>0.0187916666666667</v>
-      </c>
-      <c r="M88" s="105" t="n">
+        <v/>
+      </c>
+      <c r="M88" s="105" t="str">
         <f aca="false">IFERROR(F88*L88,"")</f>
-        <v>0.11275</v>
-      </c>
-      <c r="N88" s="106" t="n">
+        <v/>
+      </c>
+      <c r="N88" s="106" t="str">
         <f aca="false">IFERROR(J88*L88,"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O88" s="94" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="P88" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D88,1)="K",VLOOKUP(D88,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D88,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -10974,7 +10983,7 @@
         <v>901</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>428</v>
@@ -11017,7 +11026,7 @@
         <v>853.05</v>
       </c>
       <c r="O103" s="1" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="P103" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D103,1)="K",VLOOKUP(D103,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D103,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11083,7 +11092,7 @@
         <v>1.096128</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="P104" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D104,1)="K",VLOOKUP(D104,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D104,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11149,7 +11158,7 @@
         <v>0.376596</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="P105" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D105,1)="K",VLOOKUP(D105,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D105,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11162,6 +11171,58 @@
       <c r="R105" s="1" t="str">
         <f aca="false">IFERROR(IF(LEFT(D105,1)="K","rxn",VLOOKUP(D105,Additional_Supply_Catalog!$A:$K,9,FALSE())),"")</f>
         <v>mL</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F106" s="1" t="n">
+        <v>0.02708</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="H106" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F107" s="1" t="n">
+        <v>0.02708</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="H107" s="1" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -11260,7 +11321,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="85" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="B2" s="85" t="s">
         <v>901</v>
@@ -11309,7 +11370,7 @@
         <v>13018.5</v>
       </c>
       <c r="O2" s="94" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P2" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D2,1)="K",VLOOKUP(D2,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D2,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11326,7 +11387,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="85" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="B3" s="85" t="s">
         <v>901</v>
@@ -11375,7 +11436,7 @@
         <v>687.5</v>
       </c>
       <c r="O3" s="94" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P3" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D3,1)="K",VLOOKUP(D3,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D3,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11392,7 +11453,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="85" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="B4" s="85" t="s">
         <v>901</v>
@@ -11441,7 +11502,7 @@
         <v>0.31440992</v>
       </c>
       <c r="O4" s="94" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P4" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D4,1)="K",VLOOKUP(D4,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D4,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11458,13 +11519,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="85" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="B5" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C5" s="85" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="D5" s="85" t="s">
         <v>346</v>
@@ -11507,7 +11568,7 @@
         <v>2.49392</v>
       </c>
       <c r="O5" s="94" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P5" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D5,1)="K",VLOOKUP(D5,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D5,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11524,13 +11585,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="85" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="B6" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C6" s="85" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="D6" s="85" t="s">
         <v>360</v>
@@ -11573,7 +11634,7 @@
         <v>31.19116</v>
       </c>
       <c r="O6" s="94" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P6" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D6,1)="K",VLOOKUP(D6,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D6,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11590,13 +11651,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="85" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="B7" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C7" s="85" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="D7" s="85" t="s">
         <v>557</v>
@@ -11639,7 +11700,7 @@
         <v>0.85844</v>
       </c>
       <c r="O7" s="94" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="P7" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D7,1)="K",VLOOKUP(D7,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D7,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11656,13 +11717,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="85" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="B8" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C8" s="85" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="D8" s="85" t="s">
         <v>529</v>
@@ -11671,10 +11732,10 @@
         <v>22</v>
       </c>
       <c r="F8" s="86" t="n">
-        <v>1</v>
+        <v>0.02708</v>
       </c>
       <c r="G8" s="85" t="s">
-        <v>534</v>
+        <v>983</v>
       </c>
       <c r="H8" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -11686,26 +11747,26 @@
       </c>
       <c r="J8" s="89" t="n">
         <f aca="false">F8*I8*(1+H8)</f>
-        <v>8.8</v>
+        <v>0.238304</v>
       </c>
       <c r="K8" s="90" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(G8,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J8,0),ROUND(J8,2))</f>
-        <v>9</v>
-      </c>
-      <c r="L8" s="91" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L8" s="91" t="str">
         <f aca="false">IFERROR(IF(OR(D8="",P8="",Q8="",Q8=0),"",IF(VLOOKUP(R8,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G8,Unit_Conversions!$A$5:$C$28,3,FALSE()),P8*VLOOKUP(G8,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q8*VLOOKUP(R8,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
-        <v>0.03041015625</v>
-      </c>
-      <c r="M8" s="92" t="n">
+        <v/>
+      </c>
+      <c r="M8" s="92" t="str">
         <f aca="false">IFERROR(F8*L8,"")</f>
-        <v>0.03041015625</v>
-      </c>
-      <c r="N8" s="93" t="n">
+        <v/>
+      </c>
+      <c r="N8" s="93" t="str">
         <f aca="false">IFERROR(J8*L8,"")</f>
-        <v>0.267609375</v>
+        <v/>
       </c>
       <c r="O8" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P8" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D8,1)="K",VLOOKUP(D8,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D8,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11722,13 +11783,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="85" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="B9" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C9" s="85" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="D9" s="85" t="s">
         <v>536</v>
@@ -11737,10 +11798,10 @@
         <v>22</v>
       </c>
       <c r="F9" s="86" t="n">
-        <v>2</v>
+        <v>0.20312</v>
       </c>
       <c r="G9" s="85" t="s">
-        <v>534</v>
+        <v>983</v>
       </c>
       <c r="H9" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -11752,26 +11813,26 @@
       </c>
       <c r="J9" s="89" t="n">
         <f aca="false">F9*I9*(1+H9)</f>
-        <v>17.6</v>
+        <v>1.787456</v>
       </c>
       <c r="K9" s="90" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(G9,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J9,0),ROUND(J9,2))</f>
-        <v>18</v>
-      </c>
-      <c r="L9" s="91" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="L9" s="91" t="str">
         <f aca="false">IFERROR(IF(OR(D9="",P9="",Q9="",Q9=0),"",IF(VLOOKUP(R9,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G9,Unit_Conversions!$A$5:$C$28,3,FALSE()),P9*VLOOKUP(G9,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q9*VLOOKUP(R9,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
-        <v>0.0187916666666667</v>
-      </c>
-      <c r="M9" s="92" t="n">
+        <v/>
+      </c>
+      <c r="M9" s="92" t="str">
         <f aca="false">IFERROR(F9*L9,"")</f>
-        <v>0.0375833333333333</v>
-      </c>
-      <c r="N9" s="93" t="n">
+        <v/>
+      </c>
+      <c r="N9" s="93" t="str">
         <f aca="false">IFERROR(J9*L9,"")</f>
-        <v>0.330733333333333</v>
+        <v/>
       </c>
       <c r="O9" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P9" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D9,1)="K",VLOOKUP(D9,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D9,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11788,13 +11849,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="85" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="B10" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C10" s="85" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="D10" s="85" t="s">
         <v>540</v>
@@ -11803,10 +11864,10 @@
         <v>22</v>
       </c>
       <c r="F10" s="86" t="n">
-        <v>2</v>
+        <v>0.02708</v>
       </c>
       <c r="G10" s="85" t="s">
-        <v>534</v>
+        <v>983</v>
       </c>
       <c r="H10" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -11818,26 +11879,26 @@
       </c>
       <c r="J10" s="89" t="n">
         <f aca="false">F10*I10*(1+H10)</f>
-        <v>17.6</v>
+        <v>0.238304</v>
       </c>
       <c r="K10" s="90" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(G10,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J10,0),ROUND(J10,2))</f>
-        <v>18</v>
-      </c>
-      <c r="L10" s="91" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L10" s="91" t="str">
         <f aca="false">IFERROR(IF(OR(D10="",P10="",Q10="",Q10=0),"",IF(VLOOKUP(R10,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G10,Unit_Conversions!$A$5:$C$28,3,FALSE()),P10*VLOOKUP(G10,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q10*VLOOKUP(R10,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
-        <v>0.0187916666666667</v>
-      </c>
-      <c r="M10" s="92" t="n">
+        <v/>
+      </c>
+      <c r="M10" s="92" t="str">
         <f aca="false">IFERROR(F10*L10,"")</f>
-        <v>0.0375833333333333</v>
-      </c>
-      <c r="N10" s="93" t="n">
+        <v/>
+      </c>
+      <c r="N10" s="93" t="str">
         <f aca="false">IFERROR(J10*L10,"")</f>
-        <v>0.330733333333333</v>
+        <v/>
       </c>
       <c r="O10" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P10" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D10,1)="K",VLOOKUP(D10,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D10,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11854,13 +11915,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="85" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="B11" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C11" s="85" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="D11" s="85" t="s">
         <v>544</v>
@@ -11903,7 +11964,7 @@
         <v>1.580128</v>
       </c>
       <c r="O11" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P11" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D11,1)="K",VLOOKUP(D11,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D11,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11920,7 +11981,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="85" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="B12" s="85" t="s">
         <v>901</v>
@@ -11969,7 +12030,7 @@
         <v>0.00121968</v>
       </c>
       <c r="O12" s="94" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="P12" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D12,1)="K",VLOOKUP(D12,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D12,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -11986,13 +12047,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="85" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="B13" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C13" s="85" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D13" s="85"/>
       <c r="E13" s="85" t="s">
@@ -12033,7 +12094,7 @@
         <v/>
       </c>
       <c r="O13" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P13" s="1" t="str">
         <f aca="false">IFERROR(IF(LEFT(D13,1)="K",VLOOKUP(D13,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D13,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12050,7 +12111,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="96" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="B14" s="96" t="s">
         <v>901</v>
@@ -12099,7 +12160,7 @@
         <v>3437.5</v>
       </c>
       <c r="O14" s="102" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P14" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D14,1)="K",VLOOKUP(D14,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D14,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12116,7 +12177,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="96" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="B15" s="96" t="s">
         <v>901</v>
@@ -12165,7 +12226,7 @@
         <v>82.5</v>
       </c>
       <c r="O15" s="102" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P15" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D15,1)="K",VLOOKUP(D15,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D15,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12182,7 +12243,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="96" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="B16" s="96" t="s">
         <v>901</v>
@@ -12231,7 +12292,7 @@
         <v>22</v>
       </c>
       <c r="O16" s="102" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P16" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D16,1)="K",VLOOKUP(D16,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D16,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12248,7 +12309,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="85" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B17" s="85" t="s">
         <v>901</v>
@@ -12297,7 +12358,7 @@
         <v>687.5</v>
       </c>
       <c r="O17" s="94" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P17" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D17,1)="K",VLOOKUP(D17,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D17,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12314,7 +12375,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="85" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B18" s="85" t="s">
         <v>901</v>
@@ -12363,7 +12424,7 @@
         <v>88</v>
       </c>
       <c r="O18" s="94" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P18" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D18,1)="K",VLOOKUP(D18,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D18,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12380,7 +12441,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="85" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B19" s="85" t="s">
         <v>901</v>
@@ -12429,7 +12490,7 @@
         <v>0.24854192</v>
       </c>
       <c r="O19" s="94" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P19" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D19,1)="K",VLOOKUP(D19,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D19,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12446,13 +12507,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="85" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B20" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C20" s="85" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="D20" s="85" t="s">
         <v>346</v>
@@ -12495,7 +12556,7 @@
         <v>2.01432</v>
       </c>
       <c r="O20" s="94" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P20" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D20,1)="K",VLOOKUP(D20,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D20,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12512,13 +12573,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="85" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B21" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C21" s="85" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="D21" s="85" t="s">
         <v>360</v>
@@ -12561,7 +12622,7 @@
         <v>47.9864</v>
       </c>
       <c r="O21" s="94" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P21" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D21,1)="K",VLOOKUP(D21,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D21,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12578,13 +12639,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="85" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B22" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C22" s="85" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="D22" s="85" t="s">
         <v>375</v>
@@ -12596,7 +12657,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="85" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="H22" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -12627,7 +12688,7 @@
         <v/>
       </c>
       <c r="O22" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P22" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D22,1)="K",VLOOKUP(D22,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D22,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12644,13 +12705,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="85" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B23" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C23" s="85" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D23" s="85" t="s">
         <v>367</v>
@@ -12662,7 +12723,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="85" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="H23" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -12693,7 +12754,7 @@
         <v>7.50904</v>
       </c>
       <c r="O23" s="94" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P23" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D23,1)="K",VLOOKUP(D23,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D23,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12710,13 +12771,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="85" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B24" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C24" s="85" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="D24" s="85" t="s">
         <v>579</v>
@@ -12759,7 +12820,7 @@
         <v>2.376</v>
       </c>
       <c r="O24" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P24" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D24,1)="K",VLOOKUP(D24,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D24,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12776,13 +12837,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="85" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B25" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C25" s="85" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="D25" s="85" t="s">
         <v>557</v>
@@ -12825,7 +12886,7 @@
         <v>0.85844</v>
       </c>
       <c r="O25" s="94" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="P25" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D25,1)="K",VLOOKUP(D25,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D25,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12842,13 +12903,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="85" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B26" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C26" s="85" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="D26" s="85" t="s">
         <v>536</v>
@@ -12857,10 +12918,10 @@
         <v>25</v>
       </c>
       <c r="F26" s="86" t="n">
-        <v>4</v>
+        <v>0.37917</v>
       </c>
       <c r="G26" s="85" t="s">
-        <v>534</v>
+        <v>983</v>
       </c>
       <c r="H26" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -12872,26 +12933,26 @@
       </c>
       <c r="J26" s="89" t="n">
         <f aca="false">F26*I26*(1+H26)</f>
-        <v>35.2</v>
+        <v>3.336696</v>
       </c>
       <c r="K26" s="90" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(G26,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J26,0),ROUND(J26,2))</f>
-        <v>36</v>
-      </c>
-      <c r="L26" s="91" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="L26" s="91" t="str">
         <f aca="false">IFERROR(IF(OR(D26="",P26="",Q26="",Q26=0),"",IF(VLOOKUP(R26,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G26,Unit_Conversions!$A$5:$C$28,3,FALSE()),P26*VLOOKUP(G26,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q26*VLOOKUP(R26,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
-        <v>0.0187916666666667</v>
-      </c>
-      <c r="M26" s="92" t="n">
+        <v/>
+      </c>
+      <c r="M26" s="92" t="str">
         <f aca="false">IFERROR(F26*L26,"")</f>
-        <v>0.0751666666666667</v>
-      </c>
-      <c r="N26" s="93" t="n">
+        <v/>
+      </c>
+      <c r="N26" s="93" t="str">
         <f aca="false">IFERROR(J26*L26,"")</f>
-        <v>0.661466666666667</v>
+        <v/>
       </c>
       <c r="O26" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P26" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D26,1)="K",VLOOKUP(D26,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D26,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12908,13 +12969,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="85" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B27" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C27" s="85" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="D27" s="85" t="s">
         <v>540</v>
@@ -12923,10 +12984,10 @@
         <v>25</v>
       </c>
       <c r="F27" s="86" t="n">
-        <v>1</v>
+        <v>0.08125</v>
       </c>
       <c r="G27" s="85" t="s">
-        <v>534</v>
+        <v>983</v>
       </c>
       <c r="H27" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -12938,26 +12999,26 @@
       </c>
       <c r="J27" s="89" t="n">
         <f aca="false">F27*I27*(1+H27)</f>
-        <v>8.8</v>
+        <v>0.715</v>
       </c>
       <c r="K27" s="90" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(G27,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J27,0),ROUND(J27,2))</f>
-        <v>9</v>
-      </c>
-      <c r="L27" s="91" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L27" s="91" t="str">
         <f aca="false">IFERROR(IF(OR(D27="",P27="",Q27="",Q27=0),"",IF(VLOOKUP(R27,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G27,Unit_Conversions!$A$5:$C$28,3,FALSE()),P27*VLOOKUP(G27,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q27*VLOOKUP(R27,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
-        <v>0.0187916666666667</v>
-      </c>
-      <c r="M27" s="92" t="n">
+        <v/>
+      </c>
+      <c r="M27" s="92" t="str">
         <f aca="false">IFERROR(F27*L27,"")</f>
-        <v>0.0187916666666667</v>
-      </c>
-      <c r="N27" s="93" t="n">
+        <v/>
+      </c>
+      <c r="N27" s="93" t="str">
         <f aca="false">IFERROR(J27*L27,"")</f>
-        <v>0.165366666666667</v>
+        <v/>
       </c>
       <c r="O27" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P27" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D27,1)="K",VLOOKUP(D27,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D27,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -12974,13 +13035,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="85" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B28" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C28" s="85" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="D28" s="85" t="s">
         <v>544</v>
@@ -13023,7 +13084,7 @@
         <v>1.580128</v>
       </c>
       <c r="O28" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P28" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D28,1)="K",VLOOKUP(D28,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D28,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13040,13 +13101,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="85" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B29" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C29" s="85" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="D29" s="85" t="s">
         <v>388</v>
@@ -13058,7 +13119,7 @@
         <v>1</v>
       </c>
       <c r="G29" s="85" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="H29" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -13089,7 +13150,7 @@
         <v/>
       </c>
       <c r="O29" s="94" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="P29" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D29,1)="K",VLOOKUP(D29,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D29,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13106,7 +13167,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="96" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B30" s="96" t="s">
         <v>901</v>
@@ -13155,7 +13216,7 @@
         <v>687.5</v>
       </c>
       <c r="O30" s="102" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P30" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D30,1)="K",VLOOKUP(D30,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D30,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13172,7 +13233,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="96" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B31" s="96" t="s">
         <v>901</v>
@@ -13221,7 +13282,7 @@
         <v>88</v>
       </c>
       <c r="O31" s="102" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P31" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D31,1)="K",VLOOKUP(D31,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D31,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13238,7 +13299,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="96" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B32" s="96" t="s">
         <v>901</v>
@@ -13287,7 +13348,7 @@
         <v>198</v>
       </c>
       <c r="O32" s="102" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P32" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D32,1)="K",VLOOKUP(D32,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D32,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13304,7 +13365,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="96" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B33" s="96" t="s">
         <v>901</v>
@@ -13353,7 +13414,7 @@
         <v>198</v>
       </c>
       <c r="O33" s="102" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P33" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D33,1)="K",VLOOKUP(D33,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D33,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13370,7 +13431,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="96" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B34" s="96" t="s">
         <v>901</v>
@@ -13419,7 +13480,7 @@
         <v>0.29333216</v>
       </c>
       <c r="O34" s="102" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P34" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D34,1)="K",VLOOKUP(D34,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D34,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13436,13 +13497,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="96" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B35" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C35" s="96" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="D35" s="96" t="s">
         <v>346</v>
@@ -13485,7 +13546,7 @@
         <v>3.06944</v>
       </c>
       <c r="O35" s="102" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P35" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D35,1)="K",VLOOKUP(D35,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D35,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13502,13 +13563,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="96" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B36" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C36" s="96" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="D36" s="96" t="s">
         <v>360</v>
@@ -13551,7 +13612,7 @@
         <v>76.77824</v>
       </c>
       <c r="O36" s="102" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P36" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D36,1)="K",VLOOKUP(D36,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D36,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13568,13 +13629,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="96" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B37" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C37" s="96" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="D37" s="96" t="s">
         <v>375</v>
@@ -13586,7 +13647,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="96" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="H37" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -13617,7 +13678,7 @@
         <v/>
       </c>
       <c r="O37" s="102" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P37" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D37,1)="K",VLOOKUP(D37,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D37,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13634,13 +13695,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="96" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B38" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C38" s="96" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D38" s="96" t="s">
         <v>367</v>
@@ -13652,7 +13713,7 @@
         <v>1</v>
       </c>
       <c r="G38" s="96" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="H38" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -13683,7 +13744,7 @@
         <v>7.50904</v>
       </c>
       <c r="O38" s="102" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P38" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D38,1)="K",VLOOKUP(D38,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D38,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13700,13 +13761,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="96" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B39" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C39" s="96" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="D39" s="96" t="s">
         <v>579</v>
@@ -13749,7 +13810,7 @@
         <v>2.376</v>
       </c>
       <c r="O39" s="102" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P39" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D39,1)="K",VLOOKUP(D39,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D39,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13766,13 +13827,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="96" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B40" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C40" s="96" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="D40" s="96" t="s">
         <v>557</v>
@@ -13815,7 +13876,7 @@
         <v>1.71688</v>
       </c>
       <c r="O40" s="102" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="P40" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D40,1)="K",VLOOKUP(D40,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D40,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13832,13 +13893,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="96" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B41" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C41" s="96" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="D41" s="96" t="s">
         <v>536</v>
@@ -13847,10 +13908,10 @@
         <v>27</v>
       </c>
       <c r="F41" s="97" t="n">
-        <v>5</v>
+        <v>0.54167</v>
       </c>
       <c r="G41" s="96" t="s">
-        <v>534</v>
+        <v>983</v>
       </c>
       <c r="H41" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -13862,26 +13923,26 @@
       </c>
       <c r="J41" s="100" t="n">
         <f aca="false">F41*I41*(1+H41)</f>
-        <v>44</v>
+        <v>4.766696</v>
       </c>
       <c r="K41" s="101" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(G41,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J41,0),ROUND(J41,2))</f>
-        <v>44</v>
-      </c>
-      <c r="L41" s="91" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="L41" s="91" t="str">
         <f aca="false">IFERROR(IF(OR(D41="",P41="",Q41="",Q41=0),"",IF(VLOOKUP(R41,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G41,Unit_Conversions!$A$5:$C$28,3,FALSE()),P41*VLOOKUP(G41,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q41*VLOOKUP(R41,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
-        <v>0.0187916666666667</v>
-      </c>
-      <c r="M41" s="92" t="n">
+        <v/>
+      </c>
+      <c r="M41" s="92" t="str">
         <f aca="false">IFERROR(F41*L41,"")</f>
-        <v>0.0939583333333333</v>
-      </c>
-      <c r="N41" s="93" t="n">
+        <v/>
+      </c>
+      <c r="N41" s="93" t="str">
         <f aca="false">IFERROR(J41*L41,"")</f>
-        <v>0.826833333333333</v>
+        <v/>
       </c>
       <c r="O41" s="102" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P41" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D41,1)="K",VLOOKUP(D41,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D41,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13898,13 +13959,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="96" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B42" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C42" s="96" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="D42" s="96" t="s">
         <v>540</v>
@@ -13913,10 +13974,10 @@
         <v>27</v>
       </c>
       <c r="F42" s="97" t="n">
-        <v>2</v>
+        <v>0.13542</v>
       </c>
       <c r="G42" s="96" t="s">
-        <v>534</v>
+        <v>983</v>
       </c>
       <c r="H42" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -13928,26 +13989,26 @@
       </c>
       <c r="J42" s="100" t="n">
         <f aca="false">F42*I42*(1+H42)</f>
-        <v>17.6</v>
+        <v>1.191696</v>
       </c>
       <c r="K42" s="101" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(G42,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J42,0),ROUND(J42,2))</f>
-        <v>18</v>
-      </c>
-      <c r="L42" s="91" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L42" s="91" t="str">
         <f aca="false">IFERROR(IF(OR(D42="",P42="",Q42="",Q42=0),"",IF(VLOOKUP(R42,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G42,Unit_Conversions!$A$5:$C$28,3,FALSE()),P42*VLOOKUP(G42,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q42*VLOOKUP(R42,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
-        <v>0.0187916666666667</v>
-      </c>
-      <c r="M42" s="92" t="n">
+        <v/>
+      </c>
+      <c r="M42" s="92" t="str">
         <f aca="false">IFERROR(F42*L42,"")</f>
-        <v>0.0375833333333333</v>
-      </c>
-      <c r="N42" s="93" t="n">
+        <v/>
+      </c>
+      <c r="N42" s="93" t="str">
         <f aca="false">IFERROR(J42*L42,"")</f>
-        <v>0.330733333333333</v>
+        <v/>
       </c>
       <c r="O42" s="102" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P42" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D42,1)="K",VLOOKUP(D42,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D42,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -13964,13 +14025,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="96" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B43" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C43" s="96" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="D43" s="96" t="s">
         <v>544</v>
@@ -14013,7 +14074,7 @@
         <v>1.580128</v>
       </c>
       <c r="O43" s="102" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P43" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D43,1)="K",VLOOKUP(D43,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D43,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14030,13 +14091,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="96" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B44" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C44" s="96" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D44" s="96"/>
       <c r="E44" s="96" t="s">
@@ -14077,7 +14138,7 @@
         <v/>
       </c>
       <c r="O44" s="102" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P44" s="1" t="str">
         <f aca="false">IFERROR(IF(LEFT(D44,1)="K",VLOOKUP(D44,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D44,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14094,13 +14155,13 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="96" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B45" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C45" s="96" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="D45" s="96" t="s">
         <v>388</v>
@@ -14112,7 +14173,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="96" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="H45" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -14143,7 +14204,7 @@
         <v/>
       </c>
       <c r="O45" s="102" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="P45" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D45,1)="K",VLOOKUP(D45,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D45,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14160,7 +14221,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="85" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B46" s="85" t="s">
         <v>901</v>
@@ -14209,7 +14270,7 @@
         <v>368.5</v>
       </c>
       <c r="O46" s="94" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P46" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D46,1)="K",VLOOKUP(D46,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D46,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14226,7 +14287,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="85" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B47" s="85" t="s">
         <v>901</v>
@@ -14275,7 +14336,7 @@
         <v>88</v>
       </c>
       <c r="O47" s="94" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P47" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D47,1)="K",VLOOKUP(D47,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D47,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14292,7 +14353,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="85" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B48" s="85" t="s">
         <v>901</v>
@@ -14341,7 +14402,7 @@
         <v>0.10626704</v>
       </c>
       <c r="O48" s="94" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P48" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D48,1)="K",VLOOKUP(D48,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D48,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14358,13 +14419,13 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="85" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B49" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C49" s="85" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="D49" s="85" t="s">
         <v>346</v>
@@ -14407,7 +14468,7 @@
         <v>0.9592</v>
       </c>
       <c r="O49" s="94" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P49" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D49,1)="K",VLOOKUP(D49,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D49,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14424,13 +14485,13 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="85" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B50" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C50" s="85" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="D50" s="85" t="s">
         <v>360</v>
@@ -14473,7 +14534,7 @@
         <v>28.79184</v>
       </c>
       <c r="O50" s="94" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P50" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D50,1)="K",VLOOKUP(D50,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D50,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14490,13 +14551,13 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="85" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B51" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C51" s="85" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="D51" s="85" t="s">
         <v>375</v>
@@ -14508,7 +14569,7 @@
         <v>1</v>
       </c>
       <c r="G51" s="85" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="H51" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -14539,7 +14600,7 @@
         <v/>
       </c>
       <c r="O51" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P51" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D51,1)="K",VLOOKUP(D51,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D51,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14556,13 +14617,13 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="85" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B52" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C52" s="85" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D52" s="85" t="s">
         <v>367</v>
@@ -14574,7 +14635,7 @@
         <v>1</v>
       </c>
       <c r="G52" s="85" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="H52" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -14605,7 +14666,7 @@
         <v>7.50904</v>
       </c>
       <c r="O52" s="94" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P52" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D52,1)="K",VLOOKUP(D52,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D52,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14622,13 +14683,13 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="85" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B53" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C53" s="85" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="D53" s="85" t="s">
         <v>579</v>
@@ -14671,7 +14732,7 @@
         <v>2.376</v>
       </c>
       <c r="O53" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P53" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D53,1)="K",VLOOKUP(D53,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D53,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14688,13 +14749,13 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="85" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B54" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C54" s="85" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="D54" s="85" t="s">
         <v>557</v>
@@ -14737,7 +14798,7 @@
         <v>0.85844</v>
       </c>
       <c r="O54" s="94" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="P54" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D54,1)="K",VLOOKUP(D54,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D54,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14754,13 +14815,13 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="85" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B55" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C55" s="85" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="D55" s="85" t="s">
         <v>536</v>
@@ -14769,10 +14830,10 @@
         <v>29</v>
       </c>
       <c r="F55" s="86" t="n">
-        <v>3</v>
+        <v>0.13542</v>
       </c>
       <c r="G55" s="85" t="s">
-        <v>534</v>
+        <v>983</v>
       </c>
       <c r="H55" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -14784,26 +14845,26 @@
       </c>
       <c r="J55" s="89" t="n">
         <f aca="false">F55*I55*(1+H55)</f>
-        <v>26.4</v>
+        <v>1.191696</v>
       </c>
       <c r="K55" s="90" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(G55,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J55,0),ROUND(J55,2))</f>
-        <v>27</v>
-      </c>
-      <c r="L55" s="91" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L55" s="91" t="str">
         <f aca="false">IFERROR(IF(OR(D55="",P55="",Q55="",Q55=0),"",IF(VLOOKUP(R55,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G55,Unit_Conversions!$A$5:$C$28,3,FALSE()),P55*VLOOKUP(G55,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q55*VLOOKUP(R55,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
-        <v>0.0187916666666667</v>
-      </c>
-      <c r="M55" s="92" t="n">
+        <v/>
+      </c>
+      <c r="M55" s="92" t="str">
         <f aca="false">IFERROR(F55*L55,"")</f>
-        <v>0.056375</v>
-      </c>
-      <c r="N55" s="93" t="n">
+        <v/>
+      </c>
+      <c r="N55" s="93" t="str">
         <f aca="false">IFERROR(J55*L55,"")</f>
-        <v>0.4961</v>
+        <v/>
       </c>
       <c r="O55" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P55" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D55,1)="K",VLOOKUP(D55,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D55,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14820,13 +14881,13 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="85" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B56" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C56" s="85" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="D56" s="85" t="s">
         <v>540</v>
@@ -14835,10 +14896,10 @@
         <v>29</v>
       </c>
       <c r="F56" s="86" t="n">
-        <v>1</v>
+        <v>0.02708</v>
       </c>
       <c r="G56" s="85" t="s">
-        <v>534</v>
+        <v>983</v>
       </c>
       <c r="H56" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -14850,26 +14911,26 @@
       </c>
       <c r="J56" s="89" t="n">
         <f aca="false">F56*I56*(1+H56)</f>
-        <v>8.8</v>
+        <v>0.238304</v>
       </c>
       <c r="K56" s="90" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(G56,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J56,0),ROUND(J56,2))</f>
-        <v>9</v>
-      </c>
-      <c r="L56" s="91" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L56" s="91" t="str">
         <f aca="false">IFERROR(IF(OR(D56="",P56="",Q56="",Q56=0),"",IF(VLOOKUP(R56,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G56,Unit_Conversions!$A$5:$C$28,3,FALSE()),P56*VLOOKUP(G56,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q56*VLOOKUP(R56,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
-        <v>0.0187916666666667</v>
-      </c>
-      <c r="M56" s="92" t="n">
+        <v/>
+      </c>
+      <c r="M56" s="92" t="str">
         <f aca="false">IFERROR(F56*L56,"")</f>
-        <v>0.0187916666666667</v>
-      </c>
-      <c r="N56" s="93" t="n">
+        <v/>
+      </c>
+      <c r="N56" s="93" t="str">
         <f aca="false">IFERROR(J56*L56,"")</f>
-        <v>0.165366666666667</v>
+        <v/>
       </c>
       <c r="O56" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P56" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D56,1)="K",VLOOKUP(D56,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D56,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14886,13 +14947,13 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="85" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B57" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C57" s="85" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="D57" s="85" t="s">
         <v>544</v>
@@ -14935,7 +14996,7 @@
         <v>1.580128</v>
       </c>
       <c r="O57" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P57" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D57,1)="K",VLOOKUP(D57,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D57,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -14952,13 +15013,13 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="85" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B58" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C58" s="85" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="D58" s="85" t="s">
         <v>388</v>
@@ -14970,7 +15031,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="85" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="H58" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -15001,7 +15062,7 @@
         <v/>
       </c>
       <c r="O58" s="94" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="P58" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D58,1)="K",VLOOKUP(D58,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D58,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15018,7 +15079,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="96" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B59" s="96" t="s">
         <v>901</v>
@@ -15067,7 +15128,7 @@
         <v>0.04479024</v>
       </c>
       <c r="O59" s="102" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P59" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D59,1)="K",VLOOKUP(D59,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D59,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15084,13 +15145,13 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="96" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B60" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C60" s="96" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="D60" s="96" t="s">
         <v>346</v>
@@ -15133,7 +15194,7 @@
         <v>0.52756</v>
       </c>
       <c r="O60" s="102" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P60" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D60,1)="K",VLOOKUP(D60,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D60,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15150,13 +15211,13 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="96" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B61" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C61" s="96" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="D61" s="96" t="s">
         <v>360</v>
@@ -15199,7 +15260,7 @@
         <v>20.934067</v>
       </c>
       <c r="O61" s="102" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P61" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D61,1)="K",VLOOKUP(D61,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D61,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15216,13 +15277,13 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="96" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B62" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C62" s="96" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="D62" s="96" t="s">
         <v>375</v>
@@ -15234,7 +15295,7 @@
         <v>1</v>
       </c>
       <c r="G62" s="96" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="H62" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -15265,7 +15326,7 @@
         <v/>
       </c>
       <c r="O62" s="102" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P62" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D62,1)="K",VLOOKUP(D62,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D62,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15282,13 +15343,13 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="96" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B63" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C63" s="96" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D63" s="96" t="s">
         <v>367</v>
@@ -15300,7 +15361,7 @@
         <v>1</v>
       </c>
       <c r="G63" s="96" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="H63" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -15331,7 +15392,7 @@
         <v>1.87726</v>
       </c>
       <c r="O63" s="102" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P63" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D63,1)="K",VLOOKUP(D63,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D63,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15348,13 +15409,13 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="96" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B64" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C64" s="96" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="D64" s="96" t="s">
         <v>579</v>
@@ -15397,7 +15458,7 @@
         <v>0.594</v>
       </c>
       <c r="O64" s="102" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P64" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D64,1)="K",VLOOKUP(D64,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D64,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15414,13 +15475,13 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="96" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B65" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C65" s="96" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="D65" s="96" t="s">
         <v>557</v>
@@ -15463,7 +15524,7 @@
         <v>0.42922</v>
       </c>
       <c r="O65" s="102" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="P65" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D65,1)="K",VLOOKUP(D65,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D65,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15480,13 +15541,13 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="96" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B66" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C66" s="96" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="D66" s="96" t="s">
         <v>536</v>
@@ -15495,10 +15556,10 @@
         <v>33</v>
       </c>
       <c r="F66" s="97" t="n">
-        <v>4</v>
+        <v>0.13542</v>
       </c>
       <c r="G66" s="96" t="s">
-        <v>534</v>
+        <v>983</v>
       </c>
       <c r="H66" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -15510,26 +15571,26 @@
       </c>
       <c r="J66" s="100" t="n">
         <f aca="false">F66*I66*(1+H66)</f>
-        <v>8.8</v>
+        <v>0.297924</v>
       </c>
       <c r="K66" s="101" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(G66,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J66,0),ROUND(J66,2))</f>
-        <v>9</v>
-      </c>
-      <c r="L66" s="91" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L66" s="91" t="str">
         <f aca="false">IFERROR(IF(OR(D66="",P66="",Q66="",Q66=0),"",IF(VLOOKUP(R66,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G66,Unit_Conversions!$A$5:$C$28,3,FALSE()),P66*VLOOKUP(G66,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q66*VLOOKUP(R66,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
-        <v>0.0187916666666667</v>
-      </c>
-      <c r="M66" s="92" t="n">
+        <v/>
+      </c>
+      <c r="M66" s="92" t="str">
         <f aca="false">IFERROR(F66*L66,"")</f>
-        <v>0.0751666666666667</v>
-      </c>
-      <c r="N66" s="93" t="n">
+        <v/>
+      </c>
+      <c r="N66" s="93" t="str">
         <f aca="false">IFERROR(J66*L66,"")</f>
-        <v>0.165366666666667</v>
+        <v/>
       </c>
       <c r="O66" s="102" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P66" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D66,1)="K",VLOOKUP(D66,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D66,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15546,13 +15607,13 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="96" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B67" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C67" s="96" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="D67" s="96" t="s">
         <v>540</v>
@@ -15561,10 +15622,10 @@
         <v>33</v>
       </c>
       <c r="F67" s="97" t="n">
-        <v>2</v>
+        <v>0.04063</v>
       </c>
       <c r="G67" s="96" t="s">
-        <v>534</v>
+        <v>983</v>
       </c>
       <c r="H67" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -15576,26 +15637,26 @@
       </c>
       <c r="J67" s="100" t="n">
         <f aca="false">F67*I67*(1+H67)</f>
-        <v>4.4</v>
+        <v>0.089386</v>
       </c>
       <c r="K67" s="101" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(G67,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J67,0),ROUND(J67,2))</f>
-        <v>5</v>
-      </c>
-      <c r="L67" s="91" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L67" s="91" t="str">
         <f aca="false">IFERROR(IF(OR(D67="",P67="",Q67="",Q67=0),"",IF(VLOOKUP(R67,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G67,Unit_Conversions!$A$5:$C$28,3,FALSE()),P67*VLOOKUP(G67,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q67*VLOOKUP(R67,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
-        <v>0.0187916666666667</v>
-      </c>
-      <c r="M67" s="92" t="n">
+        <v/>
+      </c>
+      <c r="M67" s="92" t="str">
         <f aca="false">IFERROR(F67*L67,"")</f>
-        <v>0.0375833333333333</v>
-      </c>
-      <c r="N67" s="93" t="n">
+        <v/>
+      </c>
+      <c r="N67" s="93" t="str">
         <f aca="false">IFERROR(J67*L67,"")</f>
-        <v>0.0826833333333333</v>
+        <v/>
       </c>
       <c r="O67" s="102" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P67" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D67,1)="K",VLOOKUP(D67,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D67,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15612,13 +15673,13 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="96" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B68" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C68" s="96" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="D68" s="96" t="s">
         <v>544</v>
@@ -15661,7 +15722,7 @@
         <v>0.395032</v>
       </c>
       <c r="O68" s="102" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P68" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D68,1)="K",VLOOKUP(D68,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D68,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15678,13 +15739,13 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="96" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B69" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C69" s="96" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="D69" s="96" t="s">
         <v>388</v>
@@ -15696,7 +15757,7 @@
         <v>1</v>
       </c>
       <c r="G69" s="96" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="H69" s="98" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -15727,7 +15788,7 @@
         <v/>
       </c>
       <c r="O69" s="102" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="P69" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D69,1)="K",VLOOKUP(D69,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D69,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15744,13 +15805,13 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="96" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B70" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C70" s="96" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="D70" s="96" t="s">
         <v>614</v>
@@ -15793,7 +15854,7 @@
         <v/>
       </c>
       <c r="O70" s="102" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P70" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D70,1)="K",VLOOKUP(D70,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D70,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15810,13 +15871,13 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="96" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B71" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C71" s="96" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="D71" s="96" t="s">
         <v>619</v>
@@ -15859,7 +15920,7 @@
         <v/>
       </c>
       <c r="O71" s="102" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P71" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D71,1)="K",VLOOKUP(D71,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D71,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15876,13 +15937,13 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="96" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B72" s="96" t="s">
         <v>901</v>
       </c>
       <c r="C72" s="96" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="D72" s="96" t="s">
         <v>435</v>
@@ -15925,7 +15986,7 @@
         <v/>
       </c>
       <c r="O72" s="102" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="P72" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D72,1)="K",VLOOKUP(D72,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D72,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -15942,7 +16003,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="85" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="B73" s="85" t="s">
         <v>901</v>
@@ -15991,7 +16052,7 @@
         <v>3437.5</v>
       </c>
       <c r="O73" s="94" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P73" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D73,1)="K",VLOOKUP(D73,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D73,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16008,7 +16069,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="85" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="B74" s="85" t="s">
         <v>901</v>
@@ -16057,7 +16118,7 @@
         <v>82.5</v>
       </c>
       <c r="O74" s="94" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P74" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D74,1)="K",VLOOKUP(D74,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D74,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16074,7 +16135,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="85" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="B75" s="85" t="s">
         <v>901</v>
@@ -16123,7 +16184,7 @@
         <v>22</v>
       </c>
       <c r="O75" s="94" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="P75" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D75,1)="K",VLOOKUP(D75,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D75,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16140,7 +16201,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="85" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="B76" s="85" t="s">
         <v>901</v>
@@ -16189,7 +16250,7 @@
         <v>0.05203572</v>
       </c>
       <c r="O76" s="94" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P76" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D76,1)="K",VLOOKUP(D76,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D76,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16206,13 +16267,13 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="85" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="B77" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C77" s="85" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="D77" s="85" t="s">
         <v>346</v>
@@ -16255,7 +16316,7 @@
         <v>0.62348</v>
       </c>
       <c r="O77" s="94" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P77" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D77,1)="K",VLOOKUP(D77,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D77,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16272,13 +16333,13 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="85" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="B78" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C78" s="85" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="D78" s="85" t="s">
         <v>360</v>
@@ -16321,7 +16382,7 @@
         <v>9.717246</v>
       </c>
       <c r="O78" s="94" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P78" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D78,1)="K",VLOOKUP(D78,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D78,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16338,13 +16399,13 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="85" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="B79" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C79" s="85" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="D79" s="85" t="s">
         <v>375</v>
@@ -16356,7 +16417,7 @@
         <v>1</v>
       </c>
       <c r="G79" s="85" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="H79" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -16387,7 +16448,7 @@
         <v/>
       </c>
       <c r="O79" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P79" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D79,1)="K",VLOOKUP(D79,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D79,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16404,13 +16465,13 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="85" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="B80" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C80" s="85" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D80" s="85" t="s">
         <v>367</v>
@@ -16422,7 +16483,7 @@
         <v>1</v>
       </c>
       <c r="G80" s="85" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="H80" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -16453,7 +16514,7 @@
         <v>1.87726</v>
       </c>
       <c r="O80" s="94" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="P80" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D80,1)="K",VLOOKUP(D80,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D80,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16470,13 +16531,13 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="85" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="B81" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C81" s="85" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="D81" s="85" t="s">
         <v>579</v>
@@ -16519,7 +16580,7 @@
         <v>0.594</v>
       </c>
       <c r="O81" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P81" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D81,1)="K",VLOOKUP(D81,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D81,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16536,13 +16597,13 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="85" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="B82" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C82" s="85" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="D82" s="85" t="s">
         <v>557</v>
@@ -16585,7 +16646,7 @@
         <v>0.21461</v>
       </c>
       <c r="O82" s="94" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="P82" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D82,1)="K",VLOOKUP(D82,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D82,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16602,13 +16663,13 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="85" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="B83" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C83" s="85" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="D83" s="85" t="s">
         <v>536</v>
@@ -16617,10 +16678,10 @@
         <v>31</v>
       </c>
       <c r="F83" s="86" t="n">
-        <v>3</v>
+        <v>0.24375</v>
       </c>
       <c r="G83" s="85" t="s">
-        <v>534</v>
+        <v>983</v>
       </c>
       <c r="H83" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -16632,26 +16693,26 @@
       </c>
       <c r="J83" s="89" t="n">
         <f aca="false">F83*I83*(1+H83)</f>
-        <v>6.6</v>
+        <v>0.53625</v>
       </c>
       <c r="K83" s="90" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(G83,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(J83,0),ROUND(J83,2))</f>
-        <v>7</v>
-      </c>
-      <c r="L83" s="91" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L83" s="91" t="str">
         <f aca="false">IFERROR(IF(OR(D83="",P83="",Q83="",Q83=0),"",IF(VLOOKUP(R83,Unit_Conversions!$A$5:$C$28,3,FALSE())=VLOOKUP(G83,Unit_Conversions!$A$5:$C$28,3,FALSE()),P83*VLOOKUP(G83,Unit_Conversions!$A$5:$C$28,2,FALSE())/(Q83*VLOOKUP(R83,Unit_Conversions!$A$5:$C$28,2,FALSE())),"")),"")</f>
-        <v>0.0187916666666667</v>
-      </c>
-      <c r="M83" s="92" t="n">
+        <v/>
+      </c>
+      <c r="M83" s="92" t="str">
         <f aca="false">IFERROR(F83*L83,"")</f>
-        <v>0.056375</v>
-      </c>
-      <c r="N83" s="93" t="n">
+        <v/>
+      </c>
+      <c r="N83" s="93" t="str">
         <f aca="false">IFERROR(J83*L83,"")</f>
-        <v>0.124025</v>
+        <v/>
       </c>
       <c r="O83" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P83" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D83,1)="K",VLOOKUP(D83,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D83,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16668,13 +16729,13 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="85" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="B84" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C84" s="85" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="D84" s="85" t="s">
         <v>544</v>
@@ -16717,7 +16778,7 @@
         <v>0.395032</v>
       </c>
       <c r="O84" s="94" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="P84" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D84,1)="K",VLOOKUP(D84,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D84,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16734,13 +16795,13 @@
     </row>
     <row r="85" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="85" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="B85" s="85" t="s">
         <v>896</v>
       </c>
       <c r="C85" s="85" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="D85" s="85"/>
       <c r="E85" s="85" t="s">
@@ -16761,18 +16822,18 @@
       <c r="M85" s="105"/>
       <c r="N85" s="106"/>
       <c r="O85" s="94" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="85" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="B86" s="85" t="s">
         <v>896</v>
       </c>
       <c r="C86" s="85" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="D86" s="85"/>
       <c r="E86" s="85" t="s">
@@ -16793,18 +16854,18 @@
       <c r="M86" s="105"/>
       <c r="N86" s="106"/>
       <c r="O86" s="94" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="85" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="B87" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C87" s="85" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="D87" s="85" t="s">
         <v>301</v>
@@ -16816,7 +16877,7 @@
         <v>1</v>
       </c>
       <c r="G87" s="85" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="H87" s="87" t="n">
         <f aca="false">Inputs!$B$20</f>
@@ -16847,7 +16908,7 @@
         <v>0</v>
       </c>
       <c r="O87" s="94" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="P87" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D87,1)="K",VLOOKUP(D87,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D87,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16864,7 +16925,7 @@
     </row>
     <row r="88" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="85" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="B88" s="85" t="s">
         <v>901</v>
@@ -16913,7 +16974,7 @@
         <v>0</v>
       </c>
       <c r="O88" s="94" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="P88" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D88,1)="K",VLOOKUP(D88,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D88,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16930,7 +16991,7 @@
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="85" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="B89" s="85" t="s">
         <v>901</v>
@@ -16979,7 +17040,7 @@
         <v>0</v>
       </c>
       <c r="O89" s="94" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="P89" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D89,1)="K",VLOOKUP(D89,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D89,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -16996,7 +17057,7 @@
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="85" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="B90" s="85" t="s">
         <v>901</v>
@@ -17045,7 +17106,7 @@
         <v>0</v>
       </c>
       <c r="O90" s="94" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="P90" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D90,1)="K",VLOOKUP(D90,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D90,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -17062,7 +17123,7 @@
     </row>
     <row r="91" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="85" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="B91" s="85" t="s">
         <v>901</v>
@@ -17111,7 +17172,7 @@
         <v>0</v>
       </c>
       <c r="O91" s="94" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="P91" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D91,1)="K",VLOOKUP(D91,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D91,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -17128,13 +17189,13 @@
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="85" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="B92" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C92" s="85" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="D92" s="85" t="s">
         <v>579</v>
@@ -17177,7 +17238,7 @@
         <v>0</v>
       </c>
       <c r="O92" s="94" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="P92" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D92,1)="K",VLOOKUP(D92,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D92,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -17194,13 +17255,13 @@
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="85" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="B93" s="85" t="s">
         <v>901</v>
       </c>
       <c r="C93" s="85" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="D93" s="85" t="s">
         <v>375</v>
@@ -17243,7 +17304,7 @@
         <v/>
       </c>
       <c r="O93" s="94" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="P93" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D93,1)="K",VLOOKUP(D93,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D93,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -17260,7 +17321,7 @@
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="85" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="B94" s="85" t="s">
         <v>901</v>
@@ -17309,7 +17370,7 @@
         <v>0</v>
       </c>
       <c r="O94" s="94" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="P94" s="1" t="n">
         <f aca="false">IFERROR(IF(LEFT(D94,1)="K",VLOOKUP(D94,Kit_Catalog!$A:$K,8,FALSE()),VLOOKUP(D94,Additional_Supply_Catalog!$A:$K,7,FALSE())),"")</f>
@@ -17415,7 +17476,7 @@
         <v>884</v>
       </c>
       <c r="D1" s="76" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="E1" s="76" t="s">
         <v>888</v>
@@ -17426,7 +17487,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="96" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B2" s="96"/>
       <c r="C2" s="96" t="s">
@@ -17489,11 +17550,11 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="96" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B5" s="96"/>
       <c r="C5" s="96" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="D5" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A5,Pre_GEM_Consumables!$G$2:$G$110,C5,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A5,Post_GEM_Consumables!$G$2:$G$97,C5,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -17825,11 +17886,11 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="96" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="B21" s="96"/>
       <c r="C21" s="96" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D21" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A21,Pre_GEM_Consumables!$G$2:$G$110,C21,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A21,Post_GEM_Consumables!$G$2:$G$97,C21,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18140,11 +18201,11 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="96" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="B36" s="96"/>
       <c r="C36" s="96" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D36" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A36,Pre_GEM_Consumables!$G$2:$G$110,C36,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A36,Post_GEM_Consumables!$G$2:$G$97,C36,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18203,7 +18264,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="96" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="B39" s="96"/>
       <c r="C39" s="96" t="s">
@@ -18623,7 +18684,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="96" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="B59" s="96"/>
       <c r="C59" s="96" t="s">
@@ -18644,7 +18705,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="96" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="B60" s="96"/>
       <c r="C60" s="96" t="s">
@@ -18665,11 +18726,11 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="96" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="B61" s="96"/>
       <c r="C61" s="96" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="D61" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A61,Pre_GEM_Consumables!$G$2:$G$110,C61,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A61,Post_GEM_Consumables!$G$2:$G$97,C61,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18686,11 +18747,11 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="96" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="B62" s="96"/>
       <c r="C62" s="96" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="D62" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A62,Pre_GEM_Consumables!$G$2:$G$110,C62,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A62,Post_GEM_Consumables!$G$2:$G$97,C62,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18707,7 +18768,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="96" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="B63" s="96"/>
       <c r="C63" s="96" t="s">
@@ -18728,7 +18789,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="96" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="B64" s="96"/>
       <c r="C64" s="96" t="s">
@@ -18749,7 +18810,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="96" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="B65" s="96"/>
       <c r="C65" s="96" t="s">
@@ -18757,20 +18818,20 @@
       </c>
       <c r="D65" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A65,Pre_GEM_Consumables!$G$2:$G$110,C65,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A65,Post_GEM_Consumables!$G$2:$G$97,C65,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
-        <v>8.8</v>
+        <v>0</v>
       </c>
       <c r="E65" s="108" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(C65,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(D65,0),ROUND(D65,2))</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F65" s="109" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$N$2:$N$110,Pre_GEM_Consumables!$C$2:$C$110,A65,Pre_GEM_Consumables!$G$2:$G$110,C65)+SUMIFS(Post_GEM_Consumables!$N$2:$N$97,Post_GEM_Consumables!$C$2:$C$97,A65,Post_GEM_Consumables!$G$2:$G$97,C65)</f>
-        <v>0.267609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="96" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="B66" s="96"/>
       <c r="C66" s="96" t="s">
@@ -18778,20 +18839,20 @@
       </c>
       <c r="D66" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A66,Pre_GEM_Consumables!$G$2:$G$110,C66,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A66,Post_GEM_Consumables!$G$2:$G$97,C66,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
-        <v>138.6</v>
+        <v>0</v>
       </c>
       <c r="E66" s="108" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(C66,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(D66,0),ROUND(D66,2))</f>
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="F66" s="109" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$N$2:$N$110,Pre_GEM_Consumables!$C$2:$C$110,A66,Pre_GEM_Consumables!$G$2:$G$110,C66)+SUMIFS(Post_GEM_Consumables!$N$2:$N$97,Post_GEM_Consumables!$C$2:$C$97,A66,Post_GEM_Consumables!$G$2:$G$97,C66)</f>
-        <v>2.604525</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="96" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="B67" s="96"/>
       <c r="C67" s="96" t="s">
@@ -18799,20 +18860,20 @@
       </c>
       <c r="D67" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A67,Pre_GEM_Consumables!$G$2:$G$110,C67,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A67,Post_GEM_Consumables!$G$2:$G$97,C67,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
-        <v>57.2</v>
+        <v>0</v>
       </c>
       <c r="E67" s="108" t="n">
         <f aca="false">IF(ISNUMBER(MATCH(C67,{"tube","each","plate","vial","kit","bottle","aliquot","strainer","cap","lane-rxn","tip","strip","lane","channel","library","sample"},0)),ROUNDUP(D67,0),ROUND(D67,2))</f>
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="F67" s="109" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$N$2:$N$110,Pre_GEM_Consumables!$C$2:$C$110,A67,Pre_GEM_Consumables!$G$2:$G$110,C67)+SUMIFS(Post_GEM_Consumables!$N$2:$N$97,Post_GEM_Consumables!$C$2:$C$97,A67,Post_GEM_Consumables!$G$2:$G$97,C67)</f>
-        <v>1.07488333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="96" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="B68" s="96"/>
       <c r="C68" s="96" t="s">
@@ -18833,7 +18894,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="96" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="B69" s="96"/>
       <c r="C69" s="96" t="s">
@@ -18854,11 +18915,11 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="96" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="B70" s="96"/>
       <c r="C70" s="96" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="D70" s="100" t="n">
         <f aca="false">SUMIFS(Pre_GEM_Consumables!$J$2:$J$110,Pre_GEM_Consumables!$C$2:$C$110,A70,Pre_GEM_Consumables!$G$2:$G$110,C70,Pre_GEM_Consumables!$B$2:$B$110,"Item")+SUMIFS(Post_GEM_Consumables!$J$2:$J$97,Post_GEM_Consumables!$C$2:$C$97,A70,Post_GEM_Consumables!$G$2:$G$97,C70,Post_GEM_Consumables!$B$2:$B$97,"Item")</f>
@@ -18875,7 +18936,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="96" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="B71" s="96"/>
       <c r="C71" s="96" t="s">
@@ -18896,7 +18957,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="96" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="B72" s="96"/>
       <c r="C72" s="96" t="s">
@@ -18917,7 +18978,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="96" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B73" s="96"/>
       <c r="C73" s="96" t="s">
@@ -18938,11 +18999,11 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="110" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="F75" s="111" t="n">
         <f aca="false">SUM(F2:F73)</f>
-        <v>30967.2078079393</v>
+        <v>30963.260790231</v>
       </c>
     </row>
   </sheetData>
@@ -18974,12 +19035,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18987,15 +19048,15 @@
         <v>897</v>
       </c>
       <c r="D4" s="113" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="114" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="C5" s="114" t="s">
         <v>884</v>
@@ -19003,7 +19064,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="B6" s="115" t="n">
         <v>1</v>
@@ -19014,7 +19075,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="B7" s="115" t="n">
         <v>0.01</v>
@@ -19028,15 +19089,15 @@
         <v>900</v>
       </c>
       <c r="D9" s="113" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="114" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B10" s="114" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="C10" s="114" t="s">
         <v>884</v>
@@ -19044,7 +19105,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="B11" s="115" t="n">
         <v>1</v>
@@ -19055,7 +19116,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="B12" s="115" t="n">
         <v>0.0025</v>
@@ -19069,15 +19130,15 @@
         <v>915</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="114" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B15" s="114" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="C15" s="114" t="s">
         <v>884</v>
@@ -19110,15 +19171,15 @@
         <v>939</v>
       </c>
       <c r="D19" s="113" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="114" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B20" s="114" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="C20" s="114" t="s">
         <v>884</v>
@@ -19151,15 +19212,15 @@
         <v>925</v>
       </c>
       <c r="D24" s="113" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="114" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B25" s="114" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="C25" s="114" t="s">
         <v>884</v>
@@ -19200,7 +19261,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="B29" s="115" t="n">
         <v>0.01</v>
@@ -19222,7 +19283,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="B31" s="115" t="n">
         <v>0.01</v>
@@ -19233,7 +19294,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="B32" s="115" t="n">
         <v>0.1</v>
@@ -19244,7 +19305,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="B33" s="115" t="n">
         <v>0.863</v>
@@ -19258,15 +19319,15 @@
         <v>926</v>
       </c>
       <c r="D35" s="113" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="114" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B36" s="114" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="C36" s="114" t="s">
         <v>884</v>
@@ -19307,7 +19368,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="B40" s="115" t="n">
         <v>0.1</v>
@@ -19318,7 +19379,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="B41" s="115" t="n">
         <v>0.885</v>
@@ -19332,15 +19393,15 @@
         <v>927</v>
       </c>
       <c r="D43" s="113" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="114" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B44" s="114" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="C44" s="114" t="s">
         <v>884</v>
@@ -19348,7 +19409,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="B45" s="115" t="n">
         <v>0.05</v>
@@ -19359,7 +19420,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="B46" s="115" t="n">
         <v>0.95</v>
@@ -19373,15 +19434,15 @@
         <v>940</v>
       </c>
       <c r="D48" s="113" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="114" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B49" s="114" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="C49" s="114" t="s">
         <v>884</v>
@@ -19425,7 +19486,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -19435,12 +19496,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="117" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="B2" s="117"/>
       <c r="C2" s="117"/>
@@ -19451,10 +19512,10 @@
         <v>884</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19465,7 +19526,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19476,18 +19537,18 @@
         <v>1000</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>1000000</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19498,7 +19559,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19509,18 +19570,18 @@
         <v>1000</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>0.001</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19531,7 +19592,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19542,7 +19603,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19553,7 +19614,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19564,7 +19625,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19575,7 +19636,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19586,29 +19647,29 @@
         <v>1</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19619,18 +19680,18 @@
         <v>1</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19641,7 +19702,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19652,7 +19713,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19663,51 +19724,51 @@
         <v>1</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19719,6 +19780,17 @@
       </c>
       <c r="C28" s="5" t="s">
         <v>379</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>1064</v>
       </c>
     </row>
   </sheetData>
@@ -19757,12 +19829,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="118" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19802,12 +19874,12 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19817,137 +19889,137 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
     </row>
   </sheetData>
@@ -19983,12 +20055,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="118" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20028,152 +20100,152 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
     </row>
   </sheetData>
